--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>46169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45062</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44473</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45057</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45225</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45852</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45204</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>46098</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44473</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44536</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45972</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45357</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>45099</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45926</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45649</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>45184</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44481</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44970</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>45014</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>45473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>45188</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>45077</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44512</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44733</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44500</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>44823</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44671</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45666</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44809</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>45229</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>45903</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
         <v>46161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>45614</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>46164</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>46010</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>45001</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>46111</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44995</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44995</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>45013</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44602</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44749</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44831</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44995</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45231</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44875</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>45898</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45133</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>45573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44483</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45183</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>46010</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>46009</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>46098</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>44599</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>46183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45076</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>45473</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44872</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44889</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>45225</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>46251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>44995</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>46245</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>45666</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>45852</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45852</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45345</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>44824</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>44853</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44546</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>44553</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44512</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>44866</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44468</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44476</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44628</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44599</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44824</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44467</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44719</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44536</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44466</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44480</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44496</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44585</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>44725</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44791</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44468</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44619</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44515</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>44581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44844</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44498</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>44712</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44783</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44783</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44510</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>44783</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44496</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>44683</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>44701</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>44475</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44571</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44601</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>44490</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44607</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44871</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44725</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44733</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44526</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44795</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>44827</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44463</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44768</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45231</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44602</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44706</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44837</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44838</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44872</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44797</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44725</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44496</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44789</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44467</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44605</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44473</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44641</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44848</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44480</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44616</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>44522</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44840</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44872</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44832</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44523</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44725</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44512</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>44762</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44790</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44824</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>44539</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44865</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44790</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44559</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44601</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44627</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>45362</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45517</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44474</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45483</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44858</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44964</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45110</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45456</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45165</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45181</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45181</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>44784</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>44607</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45006</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44830</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45516</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45167</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45019</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45460</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45457</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44840</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45016</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45327</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45762</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45345</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45357</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45393</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44844</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45533</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>44928</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>44945</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44847</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45672</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>44691</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45222</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45001</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>44701</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44701</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>45001</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45450</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45141</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45019</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45152</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44888</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44985</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>44831</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45208</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45362</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44678</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45124</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44964</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>44994</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45147</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44795</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45322</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45002</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45245</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45338</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>44895</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>44859</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45077</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>44793</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45316</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44603</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45226</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45601</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44797</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>45220</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44965</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>45100</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45097</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45733</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45088</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44957</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45594</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45692</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>44797</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>44852</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45209</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45328</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>44887</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45214</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>44664</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>44664</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>45281</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45281</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45478</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45483</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44760</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>44830</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44830</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45547</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45352</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44602</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>44466</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45393</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45393</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44932</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45075</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>44860</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45211</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45106</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>44889</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>46139</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45357</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>44844</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44817</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45479</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45142</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45852</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45785</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44776</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45827</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45890</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45890</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45316</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44609</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45098</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45302</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45477</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45786</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45033</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>44908</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>45902</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45595</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26132,7 +26132,7 @@
         <v>46136</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>44551</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45481</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45478</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45907</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>46140</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45177</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45366</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44978</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>44978</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44659</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45477</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>45915</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>45594</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>44602</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>44602</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>44816</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44519</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45870</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>44974</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44811</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>45925</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>44596</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>44596</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45229</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44886</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45006</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45348</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>46142</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>46142</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45328</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45328</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>44781</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44905</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>44628</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45088</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45477</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44858</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46146</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45405</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>44977</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>44977</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45184</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>46150</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45950</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45594</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>44978</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>44886</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45272</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44965</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45160</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44803</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44694</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45357</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45393</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44840</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>44895</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45205</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>44957</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>44942</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44942</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45239</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>44488</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>44467</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>44957</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45446</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45386</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>45120</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45478</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>44985</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44980</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>44549</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>44789</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44789</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>44461</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45547</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45182</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45182</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>44789</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45753</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>44551</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>44551</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44507</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>45677</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>44977</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>44909</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44859</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45565</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44781</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44886</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>46164</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>46000</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>44837</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>45196</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>44621</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>46164</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45189</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46000</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46002</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>44859</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>45013</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45967</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>44483</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45096</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45231</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>46010</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>46010</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46010</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>44987</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45154</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45174</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45457</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>45946</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>46101</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44518</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44862</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45393</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45153</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45163</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44830</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>46030</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44871</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>44696</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45247</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>44978</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45481</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45463</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>46037</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44830</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45148</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>46126</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>44823</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>46048</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45096</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46051</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>46078</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>44968</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45012</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>44817</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>44603</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45566</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45481</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45268</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>45230</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45547</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>44922</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>45350</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>45357</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>46155</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>46183</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>46183</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>46126</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>46126</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>46183</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>46073</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44495</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45322</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>44587</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45677</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>44945</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>46084</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>45125</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>46084</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>46188</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>46084</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45105</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>44481</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45191</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45231</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45205</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45348</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>44502</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45239</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>44701</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44888</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45050</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>46092</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45509</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>44838</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45214</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46098</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44694</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>44601</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46097</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46097</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44952</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45076</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>45075</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45518</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>46101</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>46101</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45169</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>44862</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46199</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>46106</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>45098</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45126</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44848</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>46199</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45362</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45168</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>46108</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>46199</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45056</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>44523</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>46107</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>44602</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>44530</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45000</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>44602</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>46199</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>46199</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>46199</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44995</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>46111</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45026</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44708</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>46244</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45180</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45071</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>46126</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>46126</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>46126</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>46126</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>45470</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>46126</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>46126</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>46126</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45666</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45215</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>45107</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>44480</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         <v>45268</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>46129</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43497,7 +43497,7 @@
         <v>46199</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45590</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>46132</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>44853</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45041</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>46132</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>45775</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45594</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45594</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>46135</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>44886</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45211</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45460</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45230</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45827</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45446</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>44712</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45230</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>45632</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>44491</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44982,7 +44982,7 @@
         <v>45223</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>46136</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>45475</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>44833</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         <v>45964</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45347,7 +45347,7 @@
         <v>45972</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45264</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44855</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>44985</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>44805</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45694</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45852</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>44985</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45138</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44888</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>44888</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>44623</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>44616</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45070</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45478</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46467,7 +46467,7 @@
         <v>46251</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46540,7 +46540,7 @@
         <v>45520</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>46248</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>44467</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>45688</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>44464</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>44596</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45238</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45692</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45214</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45189</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>45061</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>45001</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45001</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>44600</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>44957</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45646</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>44725</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>46245</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>46245</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45229</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>44824</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45016</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45328</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45103</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45204</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>44643</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>44984</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45108</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>44957</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>44934</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>44599</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>44851</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45384</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45204</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>46245</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         <v>45646</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45415</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>44483</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>45141</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49432,7 +49432,7 @@
         <v>44460</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>44461</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45071</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>46261</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>44963</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>44992</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>45169</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45153</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45329</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50099,7 +50099,7 @@
         <v>44963</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         <v>45090</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>44699</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>44582</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>44582</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>45386</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>46260</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50620,7 +50620,7 @@
         <v>45462</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45328</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>44691</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45050</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45636</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>46245</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45674</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45593</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>44825</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>46227</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45698</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>46232</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45461</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>45517</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45674</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>45646</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>45798</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45231</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>45560</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52022,7 +52022,7 @@
         <v>45798</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45240</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45799</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45799</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>46253</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45813</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45798</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45531</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45822</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45835</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45841</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45700</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45772</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>45852</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45852</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45845</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45729</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45810</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45875</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45881</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45727</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>45853</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45105</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>45257</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45098</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>45474</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45345</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>44980</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>44903</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>44658</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54272,7 +54272,7 @@
         <v>45714</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>45531</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>45798</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>45946</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>44876</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45057</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>44473</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45852</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45062</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44473</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>45357</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45972</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44536</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45649</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44481</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>44970</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45077</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>45014</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>45184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45188</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45473</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44512</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44733</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44500</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>45013</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>45903</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>44671</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>46111</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>44995</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45001</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>44823</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44809</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>46161</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>46164</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>45666</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45614</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45229</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44602</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45322</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45281</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44889</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45473</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45898</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44483</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>45183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46010</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>46009</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>45133</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45852</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44875</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>46098</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>45002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>45076</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>46183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>46251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>45225</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>45231</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>46245</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44995</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>44599</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44831</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44995</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>44749</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45573</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45666</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45345</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>44824</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>44853</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44553</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>44546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44512</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>44866</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44468</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44536</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44628</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44467</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44602</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44719</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44476</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44599</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44466</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44480</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44585</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>44725</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44791</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44619</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44468</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44515</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>44581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44844</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44498</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>44712</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44783</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44783</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44510</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>44783</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44496</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>44701</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>44683</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>44475</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44571</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44601</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>44607</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44490</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44871</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44733</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44725</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44526</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44795</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>44827</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45231</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44768</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44602</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44706</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44837</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44838</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44797</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44725</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44496</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44467</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44605</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44473</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44641</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44848</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44480</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>44616</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44522</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>44872</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44832</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44840</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44523</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44725</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44512</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44762</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44790</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44539</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44824</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44488</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45177</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44789</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44797</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44803</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44859</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44847</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45362</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44837</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45775</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44830</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44830</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>44888</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45230</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45208</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44481</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44888</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45100</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45239</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45457</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45106</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44830</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44789</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44474</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44789</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44886</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44805</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45415</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45120</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45456</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44844</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44495</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44833</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45853</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45478</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45462</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44530</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44886</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44523</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45483</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44860</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45470</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44838</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44483</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45674</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45239</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45798</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45169</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45798</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45478</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45475</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>46030</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45240</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45481</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44840</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44858</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45481</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45672</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45890</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>46037</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45890</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45088</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44602</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45646</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45560</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44602</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>44596</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45393</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45483</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45518</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45362</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45362</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>46048</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45595</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44491</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45393</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45393</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44994</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44985</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>46051</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44599</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45907</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45357</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45799</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45231</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45799</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45566</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45348</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45348</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44963</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44627</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45915</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44587</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44889</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>44502</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45925</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44957</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>46073</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45636</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>46084</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46084</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44985</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>46084</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>44980</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44659</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44995</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45594</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45594</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>46092</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>44928</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44623</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45384</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44733</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>46097</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44964</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44984</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44602</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>46097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>46098</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>46101</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>46101</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>44725</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>45950</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45272</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45247</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>46107</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>46106</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44600</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>46108</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45223</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>46111</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45762</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45316</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44797</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45565</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44701</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44701</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45594</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>46126</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>46126</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>46126</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45204</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>46126</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>44643</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45230</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45593</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45012</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45813</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45061</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45001</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45001</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45798</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45000</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>46126</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44968</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45594</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>46126</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44987</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45096</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>46132</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45666</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>46132</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45852</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45902</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45041</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>46135</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45786</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45204</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45827</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44795</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45827</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45531</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45479</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44781</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44781</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45147</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>44811</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45189</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46136</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>46000</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>46000</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>46140</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45111</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45477</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44817</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45226</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45972</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>46002</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45688</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45098</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>45182</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45182</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45785</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>46139</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>44840</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45477</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>46010</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46010</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45205</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44844</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46010</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44859</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44862</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45822</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45870</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45110</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>44895</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45209</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>44466</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44909</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>45050</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45964</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>46136</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44862</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>44582</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44963</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46142</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45211</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46142</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45231</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45520</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44852</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46146</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45076</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>44559</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45477</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44480</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>44865</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45366</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46150</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44467</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>45075</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45138</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>44848</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44887</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>44483</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>44932</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>45231</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>45229</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>45835</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45677</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45450</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45071</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45733</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45841</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45070</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44859</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44696</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45700</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45772</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44507</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>46164</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>46164</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45107</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45694</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>46101</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>45142</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>44551</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45852</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>45852</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>45393</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44992</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>45946</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>45174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45327</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45329</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45967</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>45845</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>45322</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44628</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45180</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>44601</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45097</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45019</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45463</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45446</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45393</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>46126</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>46078</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45152</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45148</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45810</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45478</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>46155</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>46126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46183</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45105</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>46126</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44621</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46183</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>45729</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>46183</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>45328</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45328</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45481</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44985</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>45328</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>46188</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45533</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45153</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>44964</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>45125</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45108</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45875</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>44596</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44596</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44582</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>44551</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>44551</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>44609</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45211</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>46199</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>46199</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45727</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45338</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46199</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45517</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>46199</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>46199</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>46199</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46199</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45881</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45632</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45230</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45077</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>45165</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>46251</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>45214</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45050</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>45692</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45674</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>44817</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45141</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45141</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>44699</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>45215</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45103</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45196</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45090</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>44678</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45446</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45238</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44664</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44664</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45124</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>44712</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>46261</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45096</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45169</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>44793</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45460</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>44823</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>44760</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45163</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45357</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44853</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>46260</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>46227</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>44518</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>44851</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45302</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>46245</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>45322</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>44895</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45268</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>46232</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>44965</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>44519</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45352</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45006</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45264</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>44886</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>44888</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45184</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45357</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45357</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45405</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45328</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45229</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44831</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>45547</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45328</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>45167</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>45026</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45478</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>46245</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>46245</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>46245</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>45181</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45181</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         <v>44776</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>44957</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>44858</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>46253</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>44602</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45016</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>46287</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>45107</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>44691</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>44601</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>46287</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>44549</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>46248</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>44942</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>44922</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>44790</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>45386</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>44905</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45002</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>44694</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>44691</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45509</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>44602</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>45006</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>44816</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44978</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45245</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>44708</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45222</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45075</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45547</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44616</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45088</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>44957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>44694</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45268</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45168</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45071</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>44830</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>44978</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44467</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45386</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>44824</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44978</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>44978</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>44977</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>44603</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44784</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>44603</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>44607</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>44701</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45019</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44871</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45160</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>44977</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45516</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>44942</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>44908</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45056</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45016</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>45191</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>45214</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45033</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45753</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45126</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>44985</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>44974</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50532,7 +50532,7 @@
         <v>44945</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45154</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45205</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>44886</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>45457</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44977</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>44855</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>44934</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>44809</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>44825</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45281</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45214</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>44830</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45316</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45646</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51642,7 +51642,7 @@
         <v>45189</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45220</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45098</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>44957</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51939,7 +51939,7 @@
         <v>44957</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>44965</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45692</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         <v>45001</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>45001</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45601</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45345</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>45013</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45594</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45677</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45646</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>44945</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45350</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45547</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>45698</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45517</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45461</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45105</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>44658</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45257</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45098</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>45474</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53585,7 +53585,7 @@
         <v>45345</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>44980</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>44903</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53829,7 +53829,7 @@
         <v>45714</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>45531</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45798</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45946</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>44876</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45225</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45057</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>44473</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45852</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>44473</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45062</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>46098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>44473</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>45357</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45972</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44536</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45649</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>44481</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>44970</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45077</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>45014</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>45184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45188</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45473</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44512</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44733</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44500</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>45013</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>45903</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>44671</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>46111</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>44995</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45001</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>44823</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44809</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>46161</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>46164</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>45666</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45614</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>45229</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44602</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45322</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45281</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44889</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45473</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45898</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44483</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>45183</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46010</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>46009</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>45133</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45852</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44875</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>46098</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>45002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>45076</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>46183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>46251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>45225</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>45231</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>46245</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44995</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>44599</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44831</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>44995</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>44749</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45573</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45666</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45103</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45345</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>44824</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>44853</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44553</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>44546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44512</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>44866</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44468</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44536</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44628</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44467</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44602</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44719</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44476</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44599</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44466</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44496</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44480</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44585</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>44725</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44791</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44619</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44468</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44515</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>44581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12352,7 +12352,7 @@
         <v>44844</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44498</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>44712</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>44783</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44783</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44510</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>44783</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>44602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44496</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>44701</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>44683</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>44475</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44571</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44601</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>44607</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44490</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44871</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>44733</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44725</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44526</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44795</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>44827</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45231</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44768</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44602</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44706</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44837</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44838</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44797</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44725</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44496</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44467</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44605</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44473</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44641</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44848</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44480</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>44616</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>44522</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>44872</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44832</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44840</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44523</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>44725</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44512</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44762</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44790</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>44539</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44824</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44488</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45177</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44789</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44797</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44803</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>44859</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44847</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45362</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44837</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45775</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44830</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>44830</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>44888</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45230</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45208</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44481</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>44888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>44888</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>45100</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>44952</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45239</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45457</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45106</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44830</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44789</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>44474</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>44789</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44886</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44805</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45415</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45120</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45456</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>44844</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45281</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>44495</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44833</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45853</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45478</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45462</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44530</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44886</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>44523</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45483</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>44860</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45470</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44838</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44483</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45674</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45239</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>45798</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45169</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45798</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45478</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45475</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>46030</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45240</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45481</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44840</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44858</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45481</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45672</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45890</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>46037</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45890</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45088</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44602</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45646</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45560</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44602</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>44596</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>45393</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45483</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45518</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45362</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45362</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>46048</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45595</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>44491</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45393</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45393</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44994</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44985</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>46051</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>44599</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>45907</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45357</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45799</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45231</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>45799</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>45566</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>45348</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45348</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44963</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44627</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45915</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44587</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>44889</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>44502</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45925</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44957</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>46073</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45636</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>46084</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46084</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>44985</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>46084</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>44980</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44659</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44995</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45594</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45594</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>46092</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>44928</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44623</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45384</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44733</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>46097</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44964</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>44984</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44602</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>46097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>46098</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>46101</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>46101</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>44725</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>45950</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45272</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45247</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>46107</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>46106</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44600</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>46108</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45223</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>46111</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45762</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>45316</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44797</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45565</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44701</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44701</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45594</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>46126</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>46126</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>46126</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45204</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>46126</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>44643</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45230</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45593</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45012</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45813</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45061</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45001</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>45001</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45798</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45000</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>46126</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44968</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>45594</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>46126</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44987</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45096</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>46132</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45666</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>46132</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45852</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45902</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45041</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>46135</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45786</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45204</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45827</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44795</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45827</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45531</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45479</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44781</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44781</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45147</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>44811</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45189</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46136</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>46000</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>46000</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>46140</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45111</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45477</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44817</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45226</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45972</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>46002</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45688</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45098</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>45182</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45182</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45785</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>46139</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>44840</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45477</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>46010</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46010</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45205</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44844</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46010</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>44859</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44862</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45822</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45870</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>45110</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>44895</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45209</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>44466</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44909</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>45050</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45964</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>46136</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44862</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>44582</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44963</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46142</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45211</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46142</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45231</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45520</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>44852</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46146</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45076</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>44559</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>45477</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44480</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>44865</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45366</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46150</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44467</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>45075</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>45138</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>44848</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44887</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>44483</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>44932</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>45231</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>45229</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>45835</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45677</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45450</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45071</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45733</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45841</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45070</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>44859</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44696</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45700</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45772</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>44507</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>46164</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>46164</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45107</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45694</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>46101</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>45142</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>44551</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>45852</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>45852</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>45393</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>44992</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35956,7 +35956,7 @@
         <v>45946</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>45174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45327</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45329</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45967</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36326,7 +36326,7 @@
         <v>45845</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36399,7 +36399,7 @@
         <v>45322</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36472,7 +36472,7 @@
         <v>44628</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45180</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>44601</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45097</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45019</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45463</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45446</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45393</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>46126</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>46078</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45152</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45148</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45810</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45478</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>46155</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>46126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46183</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45105</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>46126</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44621</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46183</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>45729</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>46183</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>45328</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45328</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45481</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44985</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>45328</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>46188</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45533</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45153</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>44964</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>45125</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45108</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45875</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>44596</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>44596</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44582</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>44551</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>44551</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>44609</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45211</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>46199</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>46199</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45727</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45338</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>46199</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45517</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>46199</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>46199</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>46199</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46199</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45881</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45632</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45230</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45077</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>45165</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40683,7 +40683,7 @@
         <v>46251</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>45214</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>45050</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>45692</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45674</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>44817</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45141</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45141</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>44699</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>45215</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>45103</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45196</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45090</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>44678</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45446</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45238</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>44664</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44664</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>45124</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>44712</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>46261</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45096</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45169</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>45153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>44793</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45460</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>44823</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>44760</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>45163</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>45357</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44853</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>46260</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>46227</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>44518</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>44851</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45302</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>46245</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>45322</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>44895</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45268</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>46232</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>44965</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>44519</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45352</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45006</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45264</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>44886</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>44888</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>45184</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45357</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45357</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45405</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>45328</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45229</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>44831</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>45547</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45328</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>45167</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>45026</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45478</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>46245</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>46245</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>46245</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>45181</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45181</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         <v>44776</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>44957</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>44858</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>46253</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>44602</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45016</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>46287</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>45107</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>44691</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>44601</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>46287</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>44549</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>46248</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>44942</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>44922</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>44790</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>45386</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>44905</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45002</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>44694</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>44691</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45509</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>44602</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>45006</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>44816</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44978</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45245</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>44708</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45222</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45075</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45547</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44616</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45088</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>44957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>44694</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45268</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45168</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45071</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>44830</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>44978</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>44467</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45386</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>44824</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44978</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>44978</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>44977</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>44603</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44784</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>44603</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>44607</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>44701</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45019</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44871</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45160</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>44977</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45516</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>44942</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>44908</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45056</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>45016</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50011,7 +50011,7 @@
         <v>45191</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>45214</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45033</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45753</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45126</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>44985</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>44974</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50532,7 +50532,7 @@
         <v>44945</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45154</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45205</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>44886</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>45457</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44977</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>44855</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>44934</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>44809</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>44825</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>45281</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45214</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>44830</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45316</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45646</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51642,7 +51642,7 @@
         <v>45189</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45220</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45098</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>44957</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51939,7 +51939,7 @@
         <v>44957</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>44965</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45692</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         <v>45001</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>45001</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45601</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45345</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>45013</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45594</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45677</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45646</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>44945</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>45350</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45547</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>45698</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45517</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45461</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45105</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>44658</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45257</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45098</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>45474</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53585,7 +53585,7 @@
         <v>45345</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>44980</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>44903</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53829,7 +53829,7 @@
         <v>45714</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>45531</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45798</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45946</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>46169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45062</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45972</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45852</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45057</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>44473</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>46098</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44473</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44536</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45926</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>45357</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45649</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45184</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>44481</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>44970</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>45014</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>45473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45188</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44512</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>44500</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>44671</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>44823</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45666</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>46010</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44809</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45903</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>46108</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>46111</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44995</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44995</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>46164</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45614</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45001</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44602</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44749</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>46010</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44831</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>46009</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45898</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>45231</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44875</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45322</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>45133</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45852</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44858</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>45573</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44483</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>46098</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>45281</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>46183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45183</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45002</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44599</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45076</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>45473</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44872</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>46245</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>46251</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45225</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>46297</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45001</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>44995</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44964</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45666</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45103</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45345</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>46297</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44824</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>44853</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44553</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44519</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>44512</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>44866</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44536</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44476</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>44599</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>44628</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44824</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>44719</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44480</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>44496</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44585</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>44725</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44791</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44619</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44515</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44844</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44498</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44712</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44783</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44783</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44783</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44510</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44496</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44701</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44683</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>44475</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44571</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44601</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44490</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44607</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44871</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44733</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>44725</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44526</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44795</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44827</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44768</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45231</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44602</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44706</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44837</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44838</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>44797</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44725</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44496</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44605</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44473</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44641</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>44848</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>44480</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44522</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44616</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44872</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44832</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44840</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>44523</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44725</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44512</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>44762</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44539</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44790</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>44824</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>44865</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45165</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45362</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45517</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>44627</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>44601</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45457</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44858</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44474</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45483</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45456</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44790</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45110</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45181</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45181</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>44784</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>44559</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>44830</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>44607</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45006</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>45460</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45516</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45167</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>44840</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45461</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45517</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45019</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>44844</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>46002</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>45016</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45327</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45762</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45393</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45001</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45345</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45357</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>46010</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>46010</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>46010</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45533</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44928</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>44847</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44691</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45222</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>44945</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45672</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45890</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45890</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44701</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>44701</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>46030</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45001</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45450</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45595</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45019</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>46037</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44888</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44809</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45907</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45141</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45152</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45674</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45646</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45798</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45231</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45560</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>46048</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45798</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45240</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45799</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>46051</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44887</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>44985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>44678</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45208</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45362</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45124</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45925</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45147</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>44964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>44795</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45322</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45002</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45245</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44895</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45338</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>46073</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44859</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44793</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45316</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45077</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45226</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>44603</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45950</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45220</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>46084</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45097</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45601</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>44797</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>46084</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>46084</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45813</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>44965</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45100</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>45088</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44852</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>46092</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44957</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45594</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44797</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45692</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45328</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46098</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45798</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45209</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46097</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45214</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44664</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44664</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45281</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45281</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>46101</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>46101</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45107</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45478</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45483</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45531</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44760</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>46107</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44932</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>46111</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45547</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44602</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44830</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>44830</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45352</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45393</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45393</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44733</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45822</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45075</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>46126</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>46126</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>44860</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46126</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>46126</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45211</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>45106</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>44889</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45357</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>46000</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44844</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>44817</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>46000</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>46132</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46132</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>46135</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45142</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>44776</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45316</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44609</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45827</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45098</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45835</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45302</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>46136</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45841</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45964</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45972</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45033</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>44908</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>44551</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45481</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45478</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45700</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45772</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>46139</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45177</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45366</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>44978</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>44978</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45852</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44659</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45594</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45479</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45852</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44602</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>44602</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>44816</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44519</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45852</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45785</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45827</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45477</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45786</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>44974</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44596</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44596</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>45902</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45229</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>44886</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45006</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46136</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45348</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45328</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45328</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45845</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>45111</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44781</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44905</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>44628</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>46140</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45088</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44858</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45405</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44977</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44977</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>45477</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>45870</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>44811</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>46142</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>46142</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45184</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45729</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45594</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45477</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44978</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44886</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>46146</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45272</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>44965</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45160</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44803</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>44694</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45810</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>46150</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45357</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45393</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44840</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>44895</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>44957</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45875</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>44942</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44942</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45239</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44488</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45677</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>46164</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>44957</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>46164</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45446</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45386</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45120</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45478</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>44985</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45967</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44980</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44549</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44789</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>44789</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45946</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46101</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45547</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45182</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45182</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>44789</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45753</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>46126</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44551</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>44551</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>45727</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45853</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46078</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44507</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44977</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>46155</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46183</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>44909</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>44859</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>46183</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>46126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>46126</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>46183</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>45565</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>44781</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>44886</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>46188</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44837</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>45196</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>44621</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>45189</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>44859</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45013</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>44483</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>45096</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>45231</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>44987</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45154</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>46199</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>46199</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>46199</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45457</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>46199</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46199</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46199</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>44518</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>44862</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45393</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45153</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>46199</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39935,7 +39935,7 @@
         <v>45163</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>44830</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         <v>44871</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44696</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45247</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44978</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>45481</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>45463</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>44830</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45148</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>44823</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>45096</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>44968</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>45012</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>44817</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46261</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>44603</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>45566</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>45481</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45268</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45230</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45547</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41551,7 +41551,7 @@
         <v>44922</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>45350</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>45357</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>46260</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>46227</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44495</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45322</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44587</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>45677</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44945</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45125</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45105</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>44481</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46232</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45191</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>45231</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45205</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45348</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44502</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45239</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44701</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>44888</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45050</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44838</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45214</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>44694</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>44601</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>44952</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45076</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45075</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45518</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>45169</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>44862</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45098</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45126</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>44848</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45362</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45168</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45056</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>46244</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>44523</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>46287</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44602</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>44530</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45000</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>44602</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>44995</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>46287</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>45026</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>44708</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>45509</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45180</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45071</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45470</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>45666</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>46126</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45215</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>45107</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>44480</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45268</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>46245</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>46248</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45590</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>46245</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>46245</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>44853</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45041</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>45775</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45594</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45594</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>46245</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46799,7 +46799,7 @@
         <v>44886</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
         <v>45211</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>45460</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47018,7 +47018,7 @@
         <v>46253</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45230</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>46295</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45446</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>44712</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>45230</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45632</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>44491</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45475</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>44833</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45264</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>44855</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>44985</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>44805</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45694</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>44985</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48352,7 +48352,7 @@
         <v>45138</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48425,7 +48425,7 @@
         <v>44888</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>44888</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>44623</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48644,7 +48644,7 @@
         <v>44616</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48717,7 +48717,7 @@
         <v>45070</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45478</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45520</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45688</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>44596</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45238</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45692</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>45214</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49316,7 +49316,7 @@
         <v>45189</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45061</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>44600</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>44957</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45646</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>44725</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45229</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>44824</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45016</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45328</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45103</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50139,7 +50139,7 @@
         <v>45204</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>44643</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50285,7 +50285,7 @@
         <v>44984</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50358,7 +50358,7 @@
         <v>45108</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50431,7 +50431,7 @@
         <v>44957</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50509,7 +50509,7 @@
         <v>44934</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>44599</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>44851</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>45384</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45204</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45646</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>45415</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>44483</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51108,7 +51108,7 @@
         <v>45141</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45071</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>44963</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>44992</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45169</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45153</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45329</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>44963</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>45090</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>44699</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>44582</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44582</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>45386</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         <v>45462</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>45328</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>44691</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45050</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45636</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52447,7 +52447,7 @@
         <v>45674</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>45593</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>44825</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52666,7 +52666,7 @@
         <v>45698</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45105</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>45257</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52885,7 +52885,7 @@
         <v>45098</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52958,7 +52958,7 @@
         <v>45474</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45345</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>44980</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>44903</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>44658</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45714</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53446,7 +53446,7 @@
         <v>45531</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45798</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45946</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>46169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>44473</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45062</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>45972</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45852</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45057</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>44473</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>46098</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>45204</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>44473</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44536</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45926</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>45357</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>45649</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45184</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>44481</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>44970</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>45014</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>45473</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45188</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44512</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>44733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>44839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>44500</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>44671</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>44823</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45666</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>46010</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44809</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45903</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>46108</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>46111</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44995</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44995</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>46164</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45614</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45001</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>44602</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44749</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>46010</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44831</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>46009</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45898</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>45231</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44875</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>45322</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>45133</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45852</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45852</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44858</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>45573</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44483</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>46098</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>45281</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>46183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45183</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>45002</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44599</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45076</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>45473</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44872</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>46245</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>46251</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45225</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>46297</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45001</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>44995</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44964</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45666</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45103</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45345</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>46297</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>44824</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>44853</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44553</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44519</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>44512</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>44866</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44536</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44476</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>44599</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>44628</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44824</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>44602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>44719</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44480</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>44496</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44585</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>44725</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44791</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44619</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44515</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44844</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44498</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44712</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44783</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44783</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44783</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44510</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>44602</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44496</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44701</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44683</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>44475</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44571</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44601</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>44490</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>44607</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44871</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44733</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>44725</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44526</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44531</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44795</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44827</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44768</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45231</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44602</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44706</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44837</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44838</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>44797</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44725</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44496</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44789</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44605</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44473</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44641</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>44848</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>44480</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44522</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>44616</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44872</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44832</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>44840</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>44523</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44725</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44512</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>44762</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44539</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>44790</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>44824</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>44865</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>45165</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>45362</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>45517</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>44627</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>44601</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45457</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44858</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44474</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45483</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>44964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45456</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>44790</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45110</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45181</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45181</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>44784</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>44559</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>44830</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>44607</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45006</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>45460</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45516</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45167</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>44840</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45461</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45517</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45019</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>44844</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>46002</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>45016</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45327</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45762</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45393</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45001</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45345</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45357</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>46010</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>46010</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>46010</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45533</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44928</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>44847</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44691</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45222</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>44945</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45672</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45890</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45890</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44701</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>44701</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>46030</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45001</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>45450</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45595</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>45019</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>46037</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44888</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44809</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45907</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45141</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45152</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45674</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45646</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45798</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45231</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45560</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>46048</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45798</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45240</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45799</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>46051</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44887</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>44985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>44831</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>44678</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45208</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45362</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45124</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45925</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45147</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>44964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>44795</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45322</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45002</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45245</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44895</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45338</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>46073</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44859</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44793</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45316</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45077</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45226</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>44603</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45950</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45220</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>46084</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45097</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45601</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>44797</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>46084</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>46084</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45813</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>44965</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45100</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>45088</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44852</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>46092</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44957</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45594</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44797</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45692</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45328</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46098</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45798</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45209</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46097</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45214</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44664</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>44664</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45281</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45281</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>46101</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>46101</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45107</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45478</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45483</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45531</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44760</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>46107</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44932</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>46111</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45547</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>44602</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44830</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>44830</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45352</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45393</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45393</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44733</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45822</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45075</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>46126</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>46126</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>44860</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46126</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>46126</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45211</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>45106</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>44889</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45357</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>46000</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>44844</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>44817</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>46000</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>46132</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>46132</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>46135</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45142</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>44776</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>45316</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44609</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45827</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45098</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45835</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45302</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>46136</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45841</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45964</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45972</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45033</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>44908</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>44551</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45481</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45478</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45700</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>45772</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>46139</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45177</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45366</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>44978</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30179,7 +30179,7 @@
         <v>44978</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>45852</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>44659</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45594</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45479</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30544,7 +30544,7 @@
         <v>45852</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44602</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>44602</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>44816</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44519</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45852</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45785</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45827</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45477</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45786</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>44974</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>44596</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44596</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>45902</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45229</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>44886</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45006</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46136</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45348</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45328</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45328</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45845</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>45111</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44781</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44905</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>44628</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>46140</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45088</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44858</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45405</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>44977</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44977</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>45477</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>45870</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>44811</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>46142</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>46142</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45184</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45729</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45594</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45477</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44978</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>44886</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>46146</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45272</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>44965</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45160</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44803</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>44694</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45810</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>46150</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45357</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45393</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44840</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>44895</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45205</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>44957</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45875</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>44942</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44942</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45239</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>44488</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45677</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>46164</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>44957</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>46164</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45446</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35490,7 +35490,7 @@
         <v>45386</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>45120</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45478</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>44985</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45967</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44980</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>44549</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>44789</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>44789</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45946</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46101</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45547</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45182</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45182</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>44789</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45753</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>46126</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>44551</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>44551</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>45727</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45853</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>46078</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44507</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44977</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>46155</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46183</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>44909</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>44859</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>46183</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>46126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>46126</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>46183</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>45565</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>44781</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>44886</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>46188</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>44837</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>45196</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>44621</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>45189</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>44859</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45013</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>44483</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>45096</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>45231</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>44987</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45154</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>46199</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>46199</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>46199</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45457</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>46199</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46199</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>46199</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>44518</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>44862</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45393</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45153</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>46199</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39935,7 +39935,7 @@
         <v>45163</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>44830</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         <v>44871</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44696</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40227,7 +40227,7 @@
         <v>45247</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44978</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>45481</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>45463</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>44830</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45148</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>44823</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>45096</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>44968</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>45012</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>44817</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46261</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>44603</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>45566</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>45481</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45268</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>45230</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45547</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41551,7 +41551,7 @@
         <v>44922</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>45350</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>45357</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>46260</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>46227</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44495</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45322</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>44587</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>45677</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>44945</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45125</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45105</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>44481</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46232</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45191</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>45231</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45205</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45348</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44502</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45239</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44701</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>44888</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45050</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44838</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45214</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>44694</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>44601</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>44952</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45076</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45075</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45518</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>45169</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>44862</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45098</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45126</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>44848</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45362</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45168</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45056</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>46244</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>44523</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>46287</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44602</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>44530</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45000</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>44602</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>44995</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>46287</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>45026</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>44708</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>45509</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45180</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45071</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45465,7 +45465,7 @@
         <v>45470</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>45666</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>46126</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45215</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
         <v>45107</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>44480</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45268</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>46245</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>46248</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45590</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>46245</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>46245</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>44853</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45041</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>45775</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45594</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45594</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>46245</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46799,7 +46799,7 @@
         <v>44886</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
         <v>45211</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>45460</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47018,7 +47018,7 @@
         <v>46253</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45230</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>46295</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45446</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>44712</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>45230</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>45632</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>44491</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45223</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         <v>45475</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>44833</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45264</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>44855</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>44985</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>44805</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>45694</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>44985</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48352,7 +48352,7 @@
         <v>45138</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48425,7 +48425,7 @@
         <v>44888</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48498,7 +48498,7 @@
         <v>44888</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>44623</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48644,7 +48644,7 @@
         <v>44616</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48717,7 +48717,7 @@
         <v>45070</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45478</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45520</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45688</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>44596</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45238</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45692</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>45214</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49316,7 +49316,7 @@
         <v>45189</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45061</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>44600</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>44957</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45646</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>44725</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45229</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>44824</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>45016</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45328</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45103</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50139,7 +50139,7 @@
         <v>45204</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>44643</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50285,7 +50285,7 @@
         <v>44984</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50358,7 +50358,7 @@
         <v>45108</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50431,7 +50431,7 @@
         <v>44957</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50509,7 +50509,7 @@
         <v>44934</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>44599</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>44851</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>45384</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45204</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>45646</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>45415</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>44483</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51108,7 +51108,7 @@
         <v>45141</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45071</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>44963</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>44992</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>45169</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51483,7 +51483,7 @@
         <v>45153</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51556,7 +51556,7 @@
         <v>45329</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>44963</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>45090</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>44699</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>44582</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>44582</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>45386</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         <v>45462</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>45328</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>44691</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45050</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45636</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52447,7 +52447,7 @@
         <v>45674</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>45593</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52593,7 +52593,7 @@
         <v>44825</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52666,7 +52666,7 @@
         <v>45698</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45105</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>45257</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52885,7 +52885,7 @@
         <v>45098</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52958,7 +52958,7 @@
         <v>45474</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45345</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53124,7 +53124,7 @@
         <v>44980</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>44903</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53295,7 +53295,7 @@
         <v>44658</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         <v>45714</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53446,7 +53446,7 @@
         <v>45531</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45798</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45946</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>44876</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45852</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45225</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45057</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>44972</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45649</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45357</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>44536</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45926</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45473</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44481</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45099</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45001</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>44970</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45077</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45014</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>45184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44512</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44733</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44500</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>44809</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>45013</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>44671</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45001</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>45229</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44823</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>46108</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>46111</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>44995</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44995</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>46010</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>46164</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44546</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44995</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44872</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44749</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45322</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>45281</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44889</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45002</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45473</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45076</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45898</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45001</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45666</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45231</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44483</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45183</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44964</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>45852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45133</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>46010</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>46009</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44995</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44858</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>46098</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>46183</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>46245</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>46251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>46297</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45103</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>45345</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>46297</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>44824</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44853</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44553</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44512</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44866</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44628</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44824</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>44599</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44602</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>44719</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44536</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44496</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>44480</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44585</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>44725</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44791</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44619</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>44515</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>44581</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>44580</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44844</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44498</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>44783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44783</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44712</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>44510</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44783</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44495</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44496</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44827</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44701</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>44683</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>44789</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>44496</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44605</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>44571</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44601</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44768</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44641</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44848</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45231</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44490</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44607</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44480</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44871</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>44602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44706</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44837</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>44838</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>44733</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44872</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44725</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44526</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>44832</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44531</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44797</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44522</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>44725</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>44840</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>44795</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44523</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44725</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>44480</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>44512</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44762</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>44790</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>44539</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44784</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>44603</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44865</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45366</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44824</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44701</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45775</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45019</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45362</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44837</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>45075</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44830</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45138</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>44888</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44871</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45160</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45230</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44848</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44977</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>44847</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45516</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>44888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44887</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44942</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>44908</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45056</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45016</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44797</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44483</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44932</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45231</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45191</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45229</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45214</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45033</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45177</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44488</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44789</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45208</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>44481</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45100</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44952</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45450</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45753</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45071</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45239</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45733</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45457</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45126</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44830</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45070</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>44985</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44805</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44859</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44803</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>44974</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44789</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44789</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44945</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44696</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45154</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>44507</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45120</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44844</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44886</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45415</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45205</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45107</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45456</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45694</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44859</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45142</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44551</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>44886</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45393</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44495</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45457</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44977</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44855</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44833</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45281</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45853</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>44934</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44809</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44825</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45281</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45478</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45462</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45327</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45329</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45214</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44830</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45316</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45322</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44628</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>44530</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45180</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45646</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>44886</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>44523</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45483</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45189</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44860</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>45470</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45220</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44838</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>44483</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>44601</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45097</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45098</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45019</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45890</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>45239</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44957</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45169</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45463</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45478</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44957</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45446</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45890</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45475</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45393</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44965</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45692</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45481</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44840</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44858</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>45601</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>45345</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45481</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>45672</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45013</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>45595</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45594</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>45677</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45088</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44602</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44602</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>44596</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>45393</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>45152</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45483</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45148</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>45646</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45518</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45907</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>44945</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>45478</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45362</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>45350</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45547</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>45460</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45362</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44491</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45393</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>45393</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44994</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>44985</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45105</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45698</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44621</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>44599</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45357</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>45915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>45328</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>45328</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45566</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>45481</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>44985</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45348</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45348</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45517</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44963</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45328</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44627</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45533</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45153</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44587</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>44889</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45461</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44502</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44964</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45125</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45925</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45108</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>44596</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>44596</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>44582</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44957</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45636</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>44551</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44551</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>44609</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45211</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45338</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45517</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45674</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44985</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45798</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45798</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>44980</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44659</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44995</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45632</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45230</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45594</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45594</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45240</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45077</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45646</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44928</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45560</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>44623</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45384</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45799</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45231</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44733</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45799</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44984</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>45165</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>44602</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45214</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>45590</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32578,7 +32578,7 @@
         <v>44725</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45050</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45272</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45247</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45692</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44600</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45674</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44817</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45141</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45141</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45813</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45798</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45223</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44699</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45215</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45103</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45950</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>45196</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45531</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45090</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45762</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45316</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44678</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>44797</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45822</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45565</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>44701</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>44701</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45594</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45204</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>44643</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45446</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45230</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45238</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45593</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45012</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45061</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45001</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45001</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45000</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>44968</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45594</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44664</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44664</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>44987</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45124</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45835</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>45096</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44712</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45666</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45096</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45169</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45841</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45153</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>44793</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45700</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45041</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45772</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45460</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45204</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44795</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>44823</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>44760</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45852</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45852</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>44781</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>44781</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45147</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45189</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45163</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45357</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>45845</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>44853</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>44817</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45226</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>44518</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>45688</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45098</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44851</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>45810</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45182</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>45182</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45302</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45322</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44895</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45729</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>44840</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45268</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45205</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44844</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45875</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44859</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44965</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>44862</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>44519</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45352</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45727</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45110</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45006</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45264</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>44886</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>44888</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45184</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>46097</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44895</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45209</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>46098</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45357</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45357</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>45405</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44909</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45050</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45328</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>46101</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>44862</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44831</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44582</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46107</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>44963</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45547</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>46106</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45328</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45211</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45167</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45026</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45231</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45520</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45478</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>44852</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46111</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45076</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>44559</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45181</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>45181</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44776</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44957</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>44858</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>46126</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>46126</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>46000</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>46000</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>44602</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>46126</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45016</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>46132</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>46002</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45107</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>46132</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44691</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>44601</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44549</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45852</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45902</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>46135</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>44942</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45786</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>44922</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44790</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45386</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44905</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46010</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>46010</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>45827</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45827</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45002</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44694</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>44691</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>46010</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45479</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>44602</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45006</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>44811</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>46136</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46140</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45111</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>44816</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>44978</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45477</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>45245</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>46030</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45972</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>44708</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45222</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>45075</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45547</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45785</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>46139</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>45477</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>44616</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45088</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>46037</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>44957</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44694</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45268</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45168</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45071</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45870</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44830</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>44978</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>45386</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>44824</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>46048</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>44978</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>44978</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45964</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>46136</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44977</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>44603</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>46051</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>46142</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>46142</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>46146</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45477</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>46150</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>46073</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46084</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46084</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>46084</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>45677</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>46092</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46097</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>46164</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>46164</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>46101</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45946</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>45174</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>45967</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>46078</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>46126</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>46183</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>46126</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>46183</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>46183</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>46188</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>46199</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>46199</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>46199</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>46199</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>46199</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>46199</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>46199</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>46227</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>46232</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>46244</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>46287</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>46287</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45509</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50814,7 +50814,7 @@
         <v>46245</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>46126</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>46248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>46245</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51106,7 +51106,7 @@
         <v>46245</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51179,7 +51179,7 @@
         <v>46245</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>46251</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>46253</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>46295</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>46301</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>46301</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>46260</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>46155</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51768,7 +51768,7 @@
         <v>46261</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51841,7 +51841,7 @@
         <v>45229</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>45105</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>44658</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>45257</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52138,7 +52138,7 @@
         <v>45098</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45474</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45345</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>44980</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>44903</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45714</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>45531</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45798</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>45946</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>44876</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46169</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45852</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45225</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45057</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45062</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>44972</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45649</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45357</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>44536</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45926</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45473</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44481</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45099</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45001</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>44970</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45077</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45014</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>45184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44512</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44733</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44500</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>44809</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>45013</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>44671</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45001</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>45229</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44823</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>46108</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>46111</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>44995</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>44995</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>46010</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>46164</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44719</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44546</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44581</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44995</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44872</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>44749</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>45322</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>45281</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44889</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45002</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45473</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45076</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45898</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45001</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45573</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>45666</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45225</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45231</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44483</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45183</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44964</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>45852</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>45133</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>46010</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>46009</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44995</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44858</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>46098</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>46183</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>46245</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>46251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>46297</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45103</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>45345</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>46297</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>44824</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44853</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44553</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44519</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44512</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44866</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44628</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>44824</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>44599</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>44602</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>44719</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44536</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44496</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>44480</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>44585</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>44725</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>44791</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44619</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>44515</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>44581</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>44580</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44844</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44498</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>44783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44783</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44712</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>44510</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44783</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44495</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44496</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44827</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44701</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>44683</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>44789</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>44496</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44605</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>44571</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44601</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44768</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44641</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44848</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45231</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44490</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44607</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44480</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44871</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>44602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44706</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44837</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>44838</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>44733</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44872</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>44725</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44526</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>44832</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44531</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44797</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44522</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>44725</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>44840</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>44795</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44523</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44725</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>44480</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>44512</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44762</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>44790</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>44539</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44784</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>44603</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44607</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44865</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45366</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44824</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44701</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45775</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45019</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45362</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44837</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>45075</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44830</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45138</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>44888</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44871</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45160</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45230</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44848</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>44977</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>44847</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45516</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>44888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44887</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44942</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>44908</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45056</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45016</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44797</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44483</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>44932</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45231</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45191</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45229</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>45214</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45033</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45177</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44488</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44789</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45208</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>44481</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>45100</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44952</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45450</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45753</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45071</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45239</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45733</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45457</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>45126</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>45106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44830</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45070</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>44985</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44805</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44859</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>44803</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>44974</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44789</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44789</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44945</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>44696</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45154</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>44507</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45120</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>44844</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44886</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45415</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45205</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45107</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45456</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45694</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44859</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45142</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44551</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>44886</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45393</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44495</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45457</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44977</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44855</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44833</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45281</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45853</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>44934</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44809</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44825</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45281</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45478</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45462</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45327</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>45329</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45214</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44830</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45316</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45322</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44628</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>44530</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45180</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45646</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>44886</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>44523</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45483</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45189</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44860</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>45470</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45220</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44838</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>44483</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>44601</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45097</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45098</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45019</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45890</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>45239</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44957</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45169</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45463</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45478</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44957</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45446</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45890</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45475</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45393</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44965</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45692</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45481</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>44840</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44858</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>45601</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>45345</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45481</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>45672</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45013</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>45595</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45594</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>45677</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45088</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44602</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>44602</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>44596</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>45393</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>45152</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>45483</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45148</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>45646</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45518</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45907</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>44945</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>45478</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>45362</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>45350</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45547</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>45460</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45362</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44491</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>45393</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>45393</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44994</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>44985</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45105</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45698</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>44621</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>44599</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27973,7 +27973,7 @@
         <v>45357</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>45915</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>45328</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28192,7 +28192,7 @@
         <v>45328</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28270,7 +28270,7 @@
         <v>45566</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         <v>45481</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>44985</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45348</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>45348</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>45517</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44963</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45328</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>44627</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45533</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45153</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44587</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>44889</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>45461</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44502</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44964</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>45125</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45925</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45108</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>44596</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>44596</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>44582</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44957</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45636</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>44551</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44551</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>44609</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45211</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45338</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45517</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45674</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44985</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45798</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45798</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>44980</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44659</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44995</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45632</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45230</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>45594</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45594</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45240</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45077</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45646</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44928</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45560</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>44623</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45384</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45799</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>45231</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44733</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45799</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>44984</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>45165</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>44602</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45214</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>45590</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32578,7 +32578,7 @@
         <v>44725</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>45050</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45272</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45247</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45692</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44600</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45674</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44817</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45141</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45141</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45813</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45798</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>45223</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44699</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45215</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45103</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45950</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>45196</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45531</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45090</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>45762</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45316</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>44678</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>44797</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45822</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45565</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>44701</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>44701</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45594</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45204</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>44643</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45446</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45230</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>45238</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45593</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45012</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45061</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45001</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45001</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45000</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>44968</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35611,7 +35611,7 @@
         <v>45594</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44664</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>44664</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>44987</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45124</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45835</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>45096</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44712</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45666</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45096</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45169</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45841</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45153</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>44793</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>45700</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45041</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45772</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45460</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45204</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44795</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>44823</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>44760</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45852</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45852</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>44781</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>44781</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>45147</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45189</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45163</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45357</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>45845</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>44853</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>44817</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45226</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>44518</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38201,7 +38201,7 @@
         <v>45688</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45098</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>44851</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>45810</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45182</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>45182</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45302</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45322</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>44895</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45729</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>44840</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45268</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45205</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>44844</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45875</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44859</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>44965</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>44862</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>44519</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45352</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45727</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45110</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45006</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45264</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>44886</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>44888</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45184</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>46097</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44895</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45209</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>46098</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45357</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45357</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>45405</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44909</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45050</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45328</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>46101</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>44862</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>44831</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>44582</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46107</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>44963</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45547</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>46106</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45328</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45211</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45167</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45026</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45231</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45520</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45478</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>44852</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46111</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45076</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>44559</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45181</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>45181</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44776</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44957</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>44858</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42699,7 +42699,7 @@
         <v>46126</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>46126</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>46000</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>46000</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>44602</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>46126</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45016</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>46132</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>46002</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45107</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>46132</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44691</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>44601</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>44549</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45852</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45902</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>46135</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>44942</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>45786</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>44922</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44790</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45386</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44905</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46010</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>46010</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>45827</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45827</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45002</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>44694</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>44691</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>46010</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45479</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>44602</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45006</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>44811</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>46136</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46140</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45111</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>44816</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>44978</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45477</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>45245</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>46030</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45972</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>44708</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45222</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>45075</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45547</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45785</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>46139</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>45477</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>44616</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45088</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>46037</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46676,7 +46676,7 @@
         <v>44957</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44694</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45268</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45168</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45071</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45870</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44830</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>44978</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>45386</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>44824</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>46048</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>44978</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>44978</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45964</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>46136</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44977</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>44603</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>46051</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>46142</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>46142</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>46146</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45477</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>46150</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>46073</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46084</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46084</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>46084</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>45677</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>46092</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46097</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>46164</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>46164</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>46101</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45946</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>45174</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>45967</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>46078</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>46126</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>46183</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>46126</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>46183</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>46183</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>46188</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>46199</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>46199</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>46199</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>46199</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>46199</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>46199</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>46199</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>46227</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>46232</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>46244</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>46287</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>46287</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45509</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50814,7 +50814,7 @@
         <v>46245</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>46126</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>46248</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>46245</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51106,7 +51106,7 @@
         <v>46245</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51179,7 +51179,7 @@
         <v>46245</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>46251</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>46253</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>46295</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51471,7 +51471,7 @@
         <v>46301</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>46301</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>46260</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>46155</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51768,7 +51768,7 @@
         <v>46261</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51841,7 +51841,7 @@
         <v>45229</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>45105</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>44658</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>45257</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52138,7 +52138,7 @@
         <v>45098</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45474</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45345</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>44980</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>44903</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45714</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>45531</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45798</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>45946</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>46169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45057</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45852</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>44536</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45357</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>44972</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45926</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>44970</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45014</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>45473</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>45001</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45077</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>44512</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44500</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>44823</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44671</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45666</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>44809</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>45903</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>46164</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>45001</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>46108</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>46111</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44995</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>44995</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45013</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>44719</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>44546</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44749</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44831</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44995</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>45231</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45898</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>45322</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>45133</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44858</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45573</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>46098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>46010</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>46009</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45281</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>45183</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>46183</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44803</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45473</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44872</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44889</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45225</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>45001</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>46245</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>46251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>44995</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44964</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>46297</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>45666</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>45852</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>45852</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>45103</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9822,7 +9822,7 @@
         <v>45345</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>46297</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44824</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44853</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44553</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>44546</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>44512</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>44866</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44599</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44824</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>44602</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>44719</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44496</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>44585</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44725</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44619</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44515</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44580</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>44844</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44498</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44712</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44783</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>44783</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44510</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44495</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44496</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44683</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44571</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44490</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44871</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44733</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44725</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44526</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44795</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45231</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44768</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44602</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44706</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44837</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44838</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44872</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44797</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44725</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44789</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44496</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44605</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44641</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44848</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>44522</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44872</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>44832</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44840</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44523</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>44725</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>44512</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>44762</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44790</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44824</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44539</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45165</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44865</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45457</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44601</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44627</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>44790</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44559</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>45362</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45483</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>45517</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44858</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45110</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>45456</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45181</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44784</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45006</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45516</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45167</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45460</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45019</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45016</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44844</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44840</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45762</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45345</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45327</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45393</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45001</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45357</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>44847</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44691</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>45222</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45533</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44928</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>44945</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45672</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>44701</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44701</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45001</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>44888</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>44809</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45019</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45141</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45152</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44985</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>44831</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45208</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45362</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>44678</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>44887</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45124</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>44964</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>44994</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>44795</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45147</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45245</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>44895</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44859</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45338</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44793</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45322</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45316</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45077</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>44603</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45226</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45002</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45220</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>45601</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44797</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45097</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>44965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45088</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45100</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45733</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45692</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44957</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45594</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44852</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>44797</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45209</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>45328</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45214</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>44664</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>44664</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>45281</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>45281</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45107</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45478</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45483</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>44760</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>44932</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>45727</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>45853</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45547</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>44602</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>46139</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>44830</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>44830</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45352</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45393</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45393</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44733</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45075</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45479</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>45852</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45785</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>45827</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44860</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>45211</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45106</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>44889</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45477</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>45357</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>45890</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>45890</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>44844</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>44817</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45786</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45902</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46136</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>45142</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45111</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>46140</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44776</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>45477</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45595</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         <v>45316</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24990,7 +24990,7 @@
         <v>44609</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45098</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45302</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45870</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45907</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44811</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>46142</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45033</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>44908</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45477</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44551</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45481</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45478</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>46146</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45177</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45366</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>44978</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45925</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>44978</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44659</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45594</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>44602</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>44602</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>44816</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44519</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46150</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>44974</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44596</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>44596</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44886</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45006</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45348</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>45328</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45328</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>44781</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44905</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44628</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45950</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45088</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>44858</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45405</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44977</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44977</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45677</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45184</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45594</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>44978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44886</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45272</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>44965</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45160</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44803</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>44694</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45357</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>46164</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>45393</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>44840</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44895</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45205</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>46164</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>44957</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44942</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>44942</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>45239</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>45967</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>44488</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>45174</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>46000</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45946</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>46101</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>45446</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30379,7 +30379,7 @@
         <v>45386</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45120</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30525,7 +30525,7 @@
         <v>46000</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30598,7 +30598,7 @@
         <v>45478</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30671,7 +30671,7 @@
         <v>44985</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>46002</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44980</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>44549</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44789</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>44789</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45547</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45182</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>45182</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>44789</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>46010</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>46010</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>45753</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>46010</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44551</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>44551</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>44507</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44977</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>44909</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>44859</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45565</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>46030</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>44781</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44886</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44837</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45196</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>44621</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>46078</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32770,7 +32770,7 @@
         <v>46037</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>45189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44859</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>46183</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45013</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>46048</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>46051</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45096</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45231</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>46183</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>46126</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>46126</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>46183</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>44987</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>45154</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45457</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>44518</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>44862</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>46188</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45393</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45153</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45163</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34401,7 +34401,7 @@
         <v>46073</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34474,7 +34474,7 @@
         <v>44830</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44871</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>44696</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45247</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>44978</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>46084</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45481</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>46084</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>46084</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>45463</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44830</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46092</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>45148</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>46098</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>46097</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>46097</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>44823</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45096</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>44968</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46101</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>46106</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>45012</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44817</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>44603</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>46199</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45566</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>46107</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45481</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>45268</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>46199</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45230</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
         <v>46199</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>46111</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36908,7 +36908,7 @@
         <v>45547</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44922</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>46199</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>46199</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>46199</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45350</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45357</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>46126</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>46126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37575,7 +37575,7 @@
         <v>44495</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
         <v>45322</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>46199</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44587</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37867,7 +37867,7 @@
         <v>46132</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>45677</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>46132</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38086,7 +38086,7 @@
         <v>44945</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45125</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45105</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45827</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45191</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38456,7 +38456,7 @@
         <v>45231</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38529,7 +38529,7 @@
         <v>45205</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>46136</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45348</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>44502</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45239</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>44701</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38967,7 +38967,7 @@
         <v>44888</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>45964</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45972</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45050</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>44838</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39337,7 +39337,7 @@
         <v>45214</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44694</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>44601</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44952</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>45076</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>45075</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>45518</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45169</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>44862</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39994,7 +39994,7 @@
         <v>45098</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40067,7 +40067,7 @@
         <v>45126</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40140,7 +40140,7 @@
         <v>44848</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>45362</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>45168</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45056</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>44523</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>44602</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>44530</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>45000</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44602</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>44995</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>45026</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>46227</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41021,7 +41021,7 @@
         <v>44708</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45180</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45071</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45470</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45666</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45215</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>45107</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>45268</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45590</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>46232</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>44853</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45041</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45775</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>45594</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45594</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44886</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45211</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45460</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45230</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45446</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>44712</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>45230</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>45632</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>44491</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>45223</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>45475</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>44833</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45264</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>44855</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>44985</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>44805</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43329,7 +43329,7 @@
         <v>45694</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>44985</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
         <v>45138</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>44888</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44888</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>44623</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>44616</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45070</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>45478</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45520</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45688</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>46244</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>44596</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44293,7 +44293,7 @@
         <v>45238</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>46287</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45692</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45214</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>45189</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45061</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>44600</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44809,7 +44809,7 @@
         <v>44957</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45646</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>44725</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45229</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>46287</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>44824</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45016</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>45328</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45103</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45204</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>44643</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>44984</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45509</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45108</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>44957</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>44934</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>44599</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>44851</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46158,7 +46158,7 @@
         <v>46126</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>45384</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45204</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>46245</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>45646</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>46248</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>46245</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>46245</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>46245</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45415</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45141</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45071</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>46253</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>44963</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>44992</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45169</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45153</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45329</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>44963</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47565,7 +47565,7 @@
         <v>45090</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>44699</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>44582</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>46251</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47862,7 +47862,7 @@
         <v>44582</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47935,7 +47935,7 @@
         <v>45386</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48008,7 +48008,7 @@
         <v>45462</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48081,7 +48081,7 @@
         <v>45328</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48159,7 +48159,7 @@
         <v>44691</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45050</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45636</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45674</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>46295</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>45593</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>46301</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>44825</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45698</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>46301</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>45461</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>45517</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49040,7 +49040,7 @@
         <v>46155</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>46260</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45674</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49264,7 +49264,7 @@
         <v>45646</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>45229</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>46261</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>45798</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>45231</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45560</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
         <v>45798</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>46307</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45240</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>45799</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45799</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50077,7 +50077,7 @@
         <v>46126</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>46135</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>46307</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50296,7 +50296,7 @@
         <v>46307</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50369,7 +50369,7 @@
         <v>45813</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45798</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50515,7 +50515,7 @@
         <v>45531</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45810</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>45822</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50734,7 +50734,7 @@
         <v>45835</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45841</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45700</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45772</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>45852</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51104,7 +51104,7 @@
         <v>45852</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45845</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45729</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45875</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45105</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45257</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45098</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>45474</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>45345</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>44980</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>44903</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>44658</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45714</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52103,7 +52103,7 @@
         <v>45531</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45798</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52249,7 +52249,7 @@
         <v>45946</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -617,13 +617,13 @@
         <v>23</v>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
         <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -638,19 +638,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R2" t="n">
         <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="T2" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="U2" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -661,6 +661,7 @@
 Knärot
 Rotfingersvamp
 Blå taggsvamp
+Brunlångöra
 Dofttaggsvamp
 Dropptaggsvamp
 Fjällig taggsvamp s.str.
@@ -675,6 +676,7 @@
 Skarp dropptaggsvamp
 Svartvit taggsvamp
 Svinrot
+Sydfladdermus
 Tallticka
 Talltita
 Ullticka
@@ -699,6 +701,8 @@
 Tjäder
 Havsörn
 Kungsfågel
+Större brunfladdermus
+Vattenfladdermus
 Huggorm
 Vanlig groda
 Vanlig padda
@@ -764,7 +768,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -892,7 +896,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1014,7 +1018,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1142,7 +1146,7 @@
         <v>46169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1259,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1368,7 +1372,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1484,7 +1488,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1599,7 @@
         <v>45057</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1714,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1834,7 @@
         <v>45852</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1945,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2050,7 +2054,7 @@
         <v>46098</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2159,7 +2163,7 @@
         <v>44536</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2271,7 +2275,7 @@
         <v>45357</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2383,7 +2387,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2491,7 +2495,7 @@
         <v>44972</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2608,7 +2612,7 @@
         <v>45926</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2720,7 @@
         <v>45649</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2824,7 +2828,7 @@
         <v>45184</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2935,7 @@
         <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3038,7 +3042,7 @@
         <v>44970</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3153,7 @@
         <v>45014</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3260,7 +3264,7 @@
         <v>45473</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3376,7 +3380,7 @@
         <v>45001</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3483,7 +3487,7 @@
         <v>45188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3599,7 @@
         <v>45077</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3707,7 +3711,7 @@
         <v>44512</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3821,7 @@
         <v>44733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3923,7 +3927,7 @@
         <v>44839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4029,7 +4033,7 @@
         <v>44500</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4139,7 +4143,7 @@
         <v>44823</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4245,7 +4249,7 @@
         <v>44671</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4355,7 +4359,7 @@
         <v>45666</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4461,7 +4465,7 @@
         <v>44809</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4567,7 +4571,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4673,7 +4677,7 @@
         <v>45903</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4784,7 +4788,7 @@
         <v>46164</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4894,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5001,7 +5005,7 @@
         <v>45614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5107,7 +5111,7 @@
         <v>45001</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5213,7 +5217,7 @@
         <v>46108</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5319,7 +5323,7 @@
         <v>46111</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5425,7 +5429,7 @@
         <v>44995</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5536,7 +5540,7 @@
         <v>44995</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5647,7 +5651,7 @@
         <v>45013</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5757,7 +5761,7 @@
         <v>44719</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5862,7 +5866,7 @@
         <v>44602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5971,7 @@
         <v>44546</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6072,7 +6076,7 @@
         <v>44581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6177,7 +6181,7 @@
         <v>44749</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6282,7 +6286,7 @@
         <v>44831</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6387,7 +6391,7 @@
         <v>44995</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6497,7 +6501,7 @@
         <v>45231</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6602,7 +6606,7 @@
         <v>45898</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6712,7 +6716,7 @@
         <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6822,7 +6826,7 @@
         <v>45322</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6927,7 +6931,7 @@
         <v>45133</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7032,7 +7036,7 @@
         <v>44858</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7141,7 +7145,7 @@
         <v>45573</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7250,7 +7254,7 @@
         <v>46098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7355,7 +7359,7 @@
         <v>46010</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7469,7 +7473,7 @@
         <v>46009</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7579,7 +7583,7 @@
         <v>45281</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7684,7 +7688,7 @@
         <v>45183</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7789,7 +7793,7 @@
         <v>46183</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7894,7 +7898,7 @@
         <v>45002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8004,7 +8008,7 @@
         <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8109,7 +8113,7 @@
         <v>45076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8214,7 +8218,7 @@
         <v>44803</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8319,7 +8323,7 @@
         <v>45473</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8429,7 +8433,7 @@
         <v>44872</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8534,7 +8538,7 @@
         <v>44889</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8639,7 +8643,7 @@
         <v>45225</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8744,7 +8748,7 @@
         <v>45001</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8849,7 +8853,7 @@
         <v>46245</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8954,7 +8958,7 @@
         <v>46251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9063,7 +9067,7 @@
         <v>44995</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9173,7 +9177,7 @@
         <v>44964</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9282,7 +9286,7 @@
         <v>46297</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9387,7 +9391,7 @@
         <v>45666</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9497,7 +9501,7 @@
         <v>45852</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9602,7 +9606,7 @@
         <v>45852</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9712,7 +9716,7 @@
         <v>45103</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9822,7 +9826,7 @@
         <v>45345</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9927,7 +9931,7 @@
         <v>46297</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10032,7 +10036,7 @@
         <v>44824</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10105,7 +10109,7 @@
         <v>44853</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10183,7 +10187,7 @@
         <v>44553</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10256,7 +10260,7 @@
         <v>44546</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10329,7 +10333,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10407,7 +10411,7 @@
         <v>44512</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10480,7 +10484,7 @@
         <v>44866</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10558,7 +10562,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10631,7 +10635,7 @@
         <v>44628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10704,7 +10708,7 @@
         <v>44599</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10777,7 +10781,7 @@
         <v>44824</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10850,7 +10854,7 @@
         <v>44602</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10923,7 +10927,7 @@
         <v>44536</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10996,7 +11000,7 @@
         <v>44719</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11069,7 +11073,7 @@
         <v>44496</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11142,7 +11146,7 @@
         <v>44585</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11215,7 +11219,7 @@
         <v>44725</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11288,7 +11292,7 @@
         <v>44791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11361,7 +11365,7 @@
         <v>44619</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11434,7 +11438,7 @@
         <v>44515</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11507,7 +11511,7 @@
         <v>44581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11580,7 +11584,7 @@
         <v>44580</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11658,7 +11662,7 @@
         <v>44844</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11731,7 +11735,7 @@
         <v>44498</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11804,7 +11808,7 @@
         <v>44712</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11877,7 +11881,7 @@
         <v>44783</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11950,7 +11954,7 @@
         <v>44783</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12023,7 +12027,7 @@
         <v>44783</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12096,7 +12100,7 @@
         <v>44510</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12174,7 +12178,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12247,7 +12251,7 @@
         <v>44495</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12320,7 +12324,7 @@
         <v>44496</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12393,7 +12397,7 @@
         <v>44683</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12466,7 +12470,7 @@
         <v>44701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12539,7 +12543,7 @@
         <v>44571</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12612,7 +12616,7 @@
         <v>44601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12685,7 +12689,7 @@
         <v>44490</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12758,7 +12762,7 @@
         <v>44607</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12831,7 +12835,7 @@
         <v>44871</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12904,7 +12908,7 @@
         <v>44733</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12977,7 +12981,7 @@
         <v>44725</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13050,7 +13054,7 @@
         <v>44526</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13123,7 +13127,7 @@
         <v>44531</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13196,7 +13200,7 @@
         <v>44795</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13269,7 +13273,7 @@
         <v>44827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13342,7 +13346,7 @@
         <v>45231</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13415,7 +13419,7 @@
         <v>44768</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13488,7 +13492,7 @@
         <v>44602</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13561,7 +13565,7 @@
         <v>44706</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13634,7 +13638,7 @@
         <v>44837</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13707,7 +13711,7 @@
         <v>44838</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13780,7 +13784,7 @@
         <v>44872</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13853,7 +13857,7 @@
         <v>44797</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13926,7 +13930,7 @@
         <v>44725</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13999,7 +14003,7 @@
         <v>44789</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14072,7 +14076,7 @@
         <v>44496</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14145,7 +14149,7 @@
         <v>44605</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14218,7 +14222,7 @@
         <v>44641</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14291,7 +14295,7 @@
         <v>44848</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14364,7 +14368,7 @@
         <v>44616</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14442,7 +14446,7 @@
         <v>44522</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14520,7 +14524,7 @@
         <v>44872</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14593,7 +14597,7 @@
         <v>44832</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14666,7 +14670,7 @@
         <v>44840</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14739,7 +14743,7 @@
         <v>44523</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14812,7 +14816,7 @@
         <v>44725</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14885,7 +14889,7 @@
         <v>44512</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14958,7 +14962,7 @@
         <v>44762</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15036,7 +15040,7 @@
         <v>44790</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15114,7 +15118,7 @@
         <v>44824</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15187,7 +15191,7 @@
         <v>44539</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15265,7 +15269,7 @@
         <v>45165</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15338,7 +15342,7 @@
         <v>44865</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15411,7 +15415,7 @@
         <v>45457</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15484,7 +15488,7 @@
         <v>44601</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15557,7 +15561,7 @@
         <v>44627</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15630,7 +15634,7 @@
         <v>44790</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15703,7 +15707,7 @@
         <v>44559</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15776,7 +15780,7 @@
         <v>45362</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15849,7 +15853,7 @@
         <v>45483</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15922,7 +15926,7 @@
         <v>45517</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15995,7 +15999,7 @@
         <v>44858</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16068,7 +16072,7 @@
         <v>44964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16141,7 +16145,7 @@
         <v>45110</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16214,7 +16218,7 @@
         <v>45456</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16287,7 +16291,7 @@
         <v>45181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16360,7 +16364,7 @@
         <v>45181</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16433,7 +16437,7 @@
         <v>44784</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16506,7 +16510,7 @@
         <v>44830</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16579,7 +16583,7 @@
         <v>44607</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16652,7 +16656,7 @@
         <v>45006</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16730,7 +16734,7 @@
         <v>45516</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16803,7 +16807,7 @@
         <v>45167</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16881,7 +16885,7 @@
         <v>45460</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16954,7 +16958,7 @@
         <v>45019</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17032,7 +17036,7 @@
         <v>45016</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17105,7 +17109,7 @@
         <v>44844</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17178,7 +17182,7 @@
         <v>44840</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17251,7 +17255,7 @@
         <v>45762</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17324,7 +17328,7 @@
         <v>45345</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17397,7 +17401,7 @@
         <v>45327</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17470,7 +17474,7 @@
         <v>45393</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17543,7 +17547,7 @@
         <v>45001</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17616,7 +17620,7 @@
         <v>45357</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17689,7 +17693,7 @@
         <v>44847</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17762,7 +17766,7 @@
         <v>44691</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17835,7 +17839,7 @@
         <v>45222</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17908,7 +17912,7 @@
         <v>45533</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17981,7 +17985,7 @@
         <v>44928</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18054,7 +18058,7 @@
         <v>44945</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18127,7 +18131,7 @@
         <v>45672</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18200,7 +18204,7 @@
         <v>44701</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18273,7 +18277,7 @@
         <v>44701</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18346,7 +18350,7 @@
         <v>45001</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18419,7 +18423,7 @@
         <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18492,7 +18496,7 @@
         <v>44888</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18565,7 +18569,7 @@
         <v>44809</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18638,7 +18642,7 @@
         <v>45019</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18716,7 +18720,7 @@
         <v>45141</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18789,7 +18793,7 @@
         <v>45152</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18862,7 +18866,7 @@
         <v>44985</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18935,7 +18939,7 @@
         <v>44831</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19008,7 +19012,7 @@
         <v>45208</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19081,7 +19085,7 @@
         <v>45362</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19154,7 +19158,7 @@
         <v>44678</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19227,7 +19231,7 @@
         <v>44887</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19300,7 +19304,7 @@
         <v>45124</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19373,7 +19377,7 @@
         <v>44964</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19446,7 +19450,7 @@
         <v>44994</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19519,7 +19523,7 @@
         <v>44795</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19592,7 +19596,7 @@
         <v>45147</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19670,7 +19674,7 @@
         <v>45245</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19748,7 +19752,7 @@
         <v>44895</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19821,7 +19825,7 @@
         <v>44859</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19894,7 +19898,7 @@
         <v>45338</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19967,7 +19971,7 @@
         <v>44793</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20040,7 +20044,7 @@
         <v>45322</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20113,7 +20117,7 @@
         <v>45316</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20186,7 +20190,7 @@
         <v>45077</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20264,7 +20268,7 @@
         <v>44603</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20337,7 +20341,7 @@
         <v>45226</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20410,7 +20414,7 @@
         <v>45002</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20483,7 +20487,7 @@
         <v>45220</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20556,7 +20560,7 @@
         <v>45601</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20629,7 +20633,7 @@
         <v>44797</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20702,7 +20706,7 @@
         <v>45097</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20775,7 +20779,7 @@
         <v>44965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20848,7 +20852,7 @@
         <v>45088</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20921,7 +20925,7 @@
         <v>45100</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20994,7 +20998,7 @@
         <v>45733</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21067,7 +21071,7 @@
         <v>45692</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21145,7 +21149,7 @@
         <v>44957</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21223,7 +21227,7 @@
         <v>45594</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21301,7 +21305,7 @@
         <v>44852</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21374,7 +21378,7 @@
         <v>44797</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21447,7 +21451,7 @@
         <v>45209</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21520,7 +21524,7 @@
         <v>45328</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21593,7 +21597,7 @@
         <v>45214</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21666,7 +21670,7 @@
         <v>44664</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21739,7 +21743,7 @@
         <v>44664</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21812,7 +21816,7 @@
         <v>45281</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21885,7 +21889,7 @@
         <v>45281</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21963,7 +21967,7 @@
         <v>45107</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22041,7 +22045,7 @@
         <v>45478</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22119,7 +22123,7 @@
         <v>45483</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22192,7 +22196,7 @@
         <v>44760</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22265,7 +22269,7 @@
         <v>44932</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22338,7 +22342,7 @@
         <v>45727</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22411,7 +22415,7 @@
         <v>45853</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22484,7 +22488,7 @@
         <v>45547</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22557,7 +22561,7 @@
         <v>44602</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22630,7 +22634,7 @@
         <v>46139</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22703,7 +22707,7 @@
         <v>44830</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22776,7 +22780,7 @@
         <v>44830</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22849,7 +22853,7 @@
         <v>45352</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22922,7 +22926,7 @@
         <v>45393</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22995,7 +22999,7 @@
         <v>45393</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23068,7 +23072,7 @@
         <v>44733</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23141,7 +23145,7 @@
         <v>45075</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23214,7 +23218,7 @@
         <v>45479</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23287,7 +23291,7 @@
         <v>45852</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23360,7 +23364,7 @@
         <v>45785</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23433,7 +23437,7 @@
         <v>45827</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23506,7 +23510,7 @@
         <v>44860</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23579,7 +23583,7 @@
         <v>45211</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23652,7 +23656,7 @@
         <v>45106</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23725,7 +23729,7 @@
         <v>44889</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23822,7 +23826,7 @@
         <v>45477</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23895,7 +23899,7 @@
         <v>45357</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23968,7 +23972,7 @@
         <v>45890</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24041,7 +24045,7 @@
         <v>45890</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24114,7 +24118,7 @@
         <v>44844</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24187,7 +24191,7 @@
         <v>44817</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24260,7 +24264,7 @@
         <v>45786</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24333,7 +24337,7 @@
         <v>45902</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24406,7 +24410,7 @@
         <v>46136</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24479,7 +24483,7 @@
         <v>45142</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24552,7 +24556,7 @@
         <v>45111</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24625,7 +24629,7 @@
         <v>46140</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24698,7 +24702,7 @@
         <v>44776</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24771,7 +24775,7 @@
         <v>45477</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24844,7 +24848,7 @@
         <v>45595</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24917,7 +24921,7 @@
         <v>45316</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24990,7 +24994,7 @@
         <v>44609</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25063,7 +25067,7 @@
         <v>45098</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25136,7 +25140,7 @@
         <v>45302</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25209,7 +25213,7 @@
         <v>45870</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25282,7 +25286,7 @@
         <v>45907</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25355,7 +25359,7 @@
         <v>44811</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25428,7 +25432,7 @@
         <v>46142</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25501,7 +25505,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25574,7 +25578,7 @@
         <v>45033</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25647,7 +25651,7 @@
         <v>44908</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25720,7 +25724,7 @@
         <v>45477</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25793,7 +25797,7 @@
         <v>44551</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25866,7 +25870,7 @@
         <v>45481</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25939,7 +25943,7 @@
         <v>45478</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26012,7 +26016,7 @@
         <v>46146</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26085,7 +26089,7 @@
         <v>45177</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26158,7 +26162,7 @@
         <v>45366</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26231,7 +26235,7 @@
         <v>44978</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26304,7 +26308,7 @@
         <v>45925</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26377,7 +26381,7 @@
         <v>44978</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26450,7 +26454,7 @@
         <v>44659</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26523,7 +26527,7 @@
         <v>45594</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26596,7 +26600,7 @@
         <v>44602</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26669,7 +26673,7 @@
         <v>44602</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26742,7 +26746,7 @@
         <v>44816</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26815,7 +26819,7 @@
         <v>44519</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26893,7 +26897,7 @@
         <v>46150</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26966,7 +26970,7 @@
         <v>44974</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27044,7 +27048,7 @@
         <v>44596</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27117,7 +27121,7 @@
         <v>44596</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27190,7 +27194,7 @@
         <v>44886</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27263,7 +27267,7 @@
         <v>45006</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27336,7 +27340,7 @@
         <v>45348</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27409,7 +27413,7 @@
         <v>45328</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27482,7 +27486,7 @@
         <v>45328</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27560,7 +27564,7 @@
         <v>44781</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27638,7 +27642,7 @@
         <v>44905</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27711,7 +27715,7 @@
         <v>44628</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27784,7 +27788,7 @@
         <v>45950</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27857,7 +27861,7 @@
         <v>45088</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27930,7 +27934,7 @@
         <v>44858</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28003,7 +28007,7 @@
         <v>45405</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28076,7 +28080,7 @@
         <v>44977</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28154,7 +28158,7 @@
         <v>44977</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28232,7 +28236,7 @@
         <v>45677</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28305,7 +28309,7 @@
         <v>45184</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28378,7 +28382,7 @@
         <v>45594</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28451,7 +28455,7 @@
         <v>44978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28524,7 +28528,7 @@
         <v>44886</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28597,7 +28601,7 @@
         <v>45272</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28670,7 +28674,7 @@
         <v>44965</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28743,7 +28747,7 @@
         <v>45160</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28821,7 +28825,7 @@
         <v>44803</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28894,7 +28898,7 @@
         <v>44694</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28967,7 +28971,7 @@
         <v>45357</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29040,7 +29044,7 @@
         <v>46164</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29113,7 +29117,7 @@
         <v>45393</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29191,7 +29195,7 @@
         <v>44840</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29264,7 +29268,7 @@
         <v>44895</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29337,7 +29341,7 @@
         <v>45205</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29410,7 +29414,7 @@
         <v>46164</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29483,7 +29487,7 @@
         <v>44957</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29556,7 +29560,7 @@
         <v>44942</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29629,7 +29633,7 @@
         <v>44942</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29702,7 +29706,7 @@
         <v>45239</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29775,7 +29779,7 @@
         <v>45967</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29848,7 +29852,7 @@
         <v>44488</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29921,7 +29925,7 @@
         <v>45174</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29999,7 +30003,7 @@
         <v>46000</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30077,7 +30081,7 @@
         <v>45946</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30150,7 +30154,7 @@
         <v>44957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30228,7 +30232,7 @@
         <v>46101</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30301,7 +30305,7 @@
         <v>45446</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30379,7 +30383,7 @@
         <v>45386</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30452,7 +30456,7 @@
         <v>45120</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30525,7 +30529,7 @@
         <v>46000</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30598,7 +30602,7 @@
         <v>45478</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30671,7 +30675,7 @@
         <v>44985</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30744,7 +30748,7 @@
         <v>46002</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30817,7 +30821,7 @@
         <v>44980</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30895,7 +30899,7 @@
         <v>44549</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30968,7 +30972,7 @@
         <v>44789</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31041,7 +31045,7 @@
         <v>44789</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31114,7 +31118,7 @@
         <v>45547</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31187,7 +31191,7 @@
         <v>45182</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31265,7 +31269,7 @@
         <v>45182</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31343,7 +31347,7 @@
         <v>44789</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31416,7 +31420,7 @@
         <v>46010</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31494,7 +31498,7 @@
         <v>46010</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31572,7 +31576,7 @@
         <v>45753</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31645,7 +31649,7 @@
         <v>46010</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31723,7 +31727,7 @@
         <v>44551</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31796,7 +31800,7 @@
         <v>44551</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31869,7 +31873,7 @@
         <v>44507</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31942,7 +31946,7 @@
         <v>44977</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32020,7 +32024,7 @@
         <v>44909</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32098,7 +32102,7 @@
         <v>44859</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32171,7 +32175,7 @@
         <v>45565</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32244,7 +32248,7 @@
         <v>46030</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32317,7 +32321,7 @@
         <v>44781</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32395,7 +32399,7 @@
         <v>44886</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32468,7 +32472,7 @@
         <v>44837</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32541,7 +32545,7 @@
         <v>45196</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32619,7 +32623,7 @@
         <v>44621</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32692,7 +32696,7 @@
         <v>46078</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32770,7 +32774,7 @@
         <v>46037</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32843,7 +32847,7 @@
         <v>45189</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32916,7 +32920,7 @@
         <v>44859</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32989,7 +32993,7 @@
         <v>46183</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33062,7 +33066,7 @@
         <v>45013</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33140,7 +33144,7 @@
         <v>46048</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33218,7 +33222,7 @@
         <v>46051</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33291,7 +33295,7 @@
         <v>45096</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33364,7 +33368,7 @@
         <v>45231</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33437,7 +33441,7 @@
         <v>46183</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33510,7 +33514,7 @@
         <v>46126</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33583,7 +33587,7 @@
         <v>46126</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33656,7 +33660,7 @@
         <v>46183</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33729,7 +33733,7 @@
         <v>44987</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33802,7 +33806,7 @@
         <v>45154</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33875,7 +33879,7 @@
         <v>45457</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33948,7 +33952,7 @@
         <v>44518</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34026,7 +34030,7 @@
         <v>44862</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34099,7 +34103,7 @@
         <v>46188</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34172,7 +34176,7 @@
         <v>45393</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34250,7 +34254,7 @@
         <v>45153</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34328,7 +34332,7 @@
         <v>45163</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34401,7 +34405,7 @@
         <v>46073</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34474,7 +34478,7 @@
         <v>44830</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34547,7 +34551,7 @@
         <v>44871</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34620,7 +34624,7 @@
         <v>44696</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34693,7 +34697,7 @@
         <v>45247</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34766,7 +34770,7 @@
         <v>44978</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34839,7 +34843,7 @@
         <v>46084</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34917,7 +34921,7 @@
         <v>45481</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34990,7 +34994,7 @@
         <v>46084</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35068,7 +35072,7 @@
         <v>46084</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35146,7 +35150,7 @@
         <v>45463</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35219,7 +35223,7 @@
         <v>44830</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35292,7 +35296,7 @@
         <v>46092</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35365,7 +35369,7 @@
         <v>45148</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35438,7 +35442,7 @@
         <v>46098</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35511,7 +35515,7 @@
         <v>46097</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35584,7 +35588,7 @@
         <v>46097</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35657,7 +35661,7 @@
         <v>44823</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35730,7 +35734,7 @@
         <v>45096</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35803,7 +35807,7 @@
         <v>44968</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35876,7 +35880,7 @@
         <v>46101</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35949,7 +35953,7 @@
         <v>46106</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36022,7 +36026,7 @@
         <v>45012</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36095,7 +36099,7 @@
         <v>44817</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36173,7 +36177,7 @@
         <v>44603</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36246,7 +36250,7 @@
         <v>46199</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36319,7 +36323,7 @@
         <v>45566</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36392,7 +36396,7 @@
         <v>46107</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36465,7 +36469,7 @@
         <v>45481</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36538,7 +36542,7 @@
         <v>45268</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36611,7 +36615,7 @@
         <v>46199</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36684,7 +36688,7 @@
         <v>45230</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36762,7 +36766,7 @@
         <v>46199</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36835,7 +36839,7 @@
         <v>46111</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36908,7 +36912,7 @@
         <v>45547</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36981,7 +36985,7 @@
         <v>44922</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37059,7 +37063,7 @@
         <v>46199</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37132,7 +37136,7 @@
         <v>46199</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37205,7 +37209,7 @@
         <v>46199</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37278,7 +37282,7 @@
         <v>45350</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37356,7 +37360,7 @@
         <v>45357</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37429,7 +37433,7 @@
         <v>46126</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37502,7 +37506,7 @@
         <v>46126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37575,7 +37579,7 @@
         <v>44495</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37648,7 +37652,7 @@
         <v>45322</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37721,7 +37725,7 @@
         <v>46199</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37794,7 +37798,7 @@
         <v>44587</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37867,7 +37871,7 @@
         <v>46132</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37940,7 +37944,7 @@
         <v>45677</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38013,7 +38017,7 @@
         <v>46132</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38086,7 +38090,7 @@
         <v>44945</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38159,7 +38163,7 @@
         <v>45125</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38232,7 +38236,7 @@
         <v>45105</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38310,7 +38314,7 @@
         <v>45827</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38383,7 +38387,7 @@
         <v>45191</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38456,7 +38460,7 @@
         <v>45231</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38529,7 +38533,7 @@
         <v>45205</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38602,7 +38606,7 @@
         <v>46136</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38675,7 +38679,7 @@
         <v>45348</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38748,7 +38752,7 @@
         <v>44502</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38821,7 +38825,7 @@
         <v>45239</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38894,7 +38898,7 @@
         <v>44701</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38967,7 +38971,7 @@
         <v>44888</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39040,7 +39044,7 @@
         <v>45964</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39113,7 +39117,7 @@
         <v>45972</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39186,7 +39190,7 @@
         <v>45050</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39264,7 +39268,7 @@
         <v>44838</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39337,7 +39341,7 @@
         <v>45214</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39410,7 +39414,7 @@
         <v>44694</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39483,7 +39487,7 @@
         <v>44601</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39556,7 +39560,7 @@
         <v>44952</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39629,7 +39633,7 @@
         <v>45076</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39702,7 +39706,7 @@
         <v>45075</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39775,7 +39779,7 @@
         <v>45518</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39848,7 +39852,7 @@
         <v>45169</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39921,7 +39925,7 @@
         <v>44862</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39994,7 +39998,7 @@
         <v>45098</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40067,7 +40071,7 @@
         <v>45126</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40140,7 +40144,7 @@
         <v>44848</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40213,7 +40217,7 @@
         <v>45362</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40286,7 +40290,7 @@
         <v>45168</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40359,7 +40363,7 @@
         <v>45056</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40432,7 +40436,7 @@
         <v>44523</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40505,7 +40509,7 @@
         <v>44602</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40578,7 +40582,7 @@
         <v>44530</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40651,7 +40655,7 @@
         <v>45000</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40724,7 +40728,7 @@
         <v>44602</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40797,7 +40801,7 @@
         <v>44995</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40875,7 +40879,7 @@
         <v>45026</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40948,7 +40952,7 @@
         <v>46227</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41021,7 +41025,7 @@
         <v>44708</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41094,7 +41098,7 @@
         <v>45180</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41167,7 +41171,7 @@
         <v>45071</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41245,7 +41249,7 @@
         <v>45470</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41318,7 +41322,7 @@
         <v>45666</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41391,7 +41395,7 @@
         <v>45215</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41464,7 +41468,7 @@
         <v>45107</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41542,7 +41546,7 @@
         <v>45268</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41615,7 +41619,7 @@
         <v>45590</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41688,7 +41692,7 @@
         <v>46232</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41766,7 +41770,7 @@
         <v>44853</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41844,7 +41848,7 @@
         <v>45041</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41917,7 +41921,7 @@
         <v>45775</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41990,7 +41994,7 @@
         <v>45594</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42068,7 +42072,7 @@
         <v>45594</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42146,7 +42150,7 @@
         <v>44886</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42219,7 +42223,7 @@
         <v>45211</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42292,7 +42296,7 @@
         <v>45460</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42365,7 +42369,7 @@
         <v>45230</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42438,7 +42442,7 @@
         <v>45446</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42516,7 +42520,7 @@
         <v>44712</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42589,7 +42593,7 @@
         <v>45230</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42667,7 +42671,7 @@
         <v>45632</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42740,7 +42744,7 @@
         <v>44491</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42813,7 +42817,7 @@
         <v>45223</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42886,7 +42890,7 @@
         <v>45475</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42959,7 +42963,7 @@
         <v>44833</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43032,7 +43036,7 @@
         <v>45264</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43105,7 +43109,7 @@
         <v>44855</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43183,7 +43187,7 @@
         <v>44985</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43256,7 +43260,7 @@
         <v>44805</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43329,7 +43333,7 @@
         <v>45694</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43402,7 +43406,7 @@
         <v>44985</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43480,7 +43484,7 @@
         <v>45138</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43553,7 +43557,7 @@
         <v>44888</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43626,7 +43630,7 @@
         <v>44888</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43699,7 +43703,7 @@
         <v>44623</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43772,7 +43776,7 @@
         <v>44616</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43845,7 +43849,7 @@
         <v>45070</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43923,7 +43927,7 @@
         <v>45478</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44001,7 +44005,7 @@
         <v>45520</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44074,7 +44078,7 @@
         <v>45688</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44147,7 +44151,7 @@
         <v>46244</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44220,7 +44224,7 @@
         <v>44596</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44293,7 +44297,7 @@
         <v>45238</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44366,7 +44370,7 @@
         <v>46287</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44439,7 +44443,7 @@
         <v>45692</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44517,7 +44521,7 @@
         <v>45214</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44590,7 +44594,7 @@
         <v>45189</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44663,7 +44667,7 @@
         <v>45061</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44736,7 +44740,7 @@
         <v>44600</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44809,7 +44813,7 @@
         <v>44957</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44887,7 +44891,7 @@
         <v>45646</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44960,7 +44964,7 @@
         <v>44725</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45033,7 +45037,7 @@
         <v>45229</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45111,7 +45115,7 @@
         <v>46287</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45184,7 +45188,7 @@
         <v>44824</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45257,7 +45261,7 @@
         <v>45016</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45335,7 +45339,7 @@
         <v>45328</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45408,7 +45412,7 @@
         <v>45103</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45486,7 +45490,7 @@
         <v>45204</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45559,7 +45563,7 @@
         <v>44643</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45632,7 +45636,7 @@
         <v>44984</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45705,7 +45709,7 @@
         <v>45509</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45783,7 +45787,7 @@
         <v>45108</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45856,7 +45860,7 @@
         <v>44957</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45934,7 +45938,7 @@
         <v>44934</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46007,7 +46011,7 @@
         <v>44599</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46080,7 +46084,7 @@
         <v>44851</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46158,7 +46162,7 @@
         <v>46126</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46231,7 +46235,7 @@
         <v>45384</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46309,7 +46313,7 @@
         <v>45204</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46387,7 +46391,7 @@
         <v>46245</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46460,7 +46464,7 @@
         <v>45646</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46533,7 +46537,7 @@
         <v>46248</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46606,7 +46610,7 @@
         <v>46245</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46679,7 +46683,7 @@
         <v>46245</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46752,7 +46756,7 @@
         <v>46245</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46825,7 +46829,7 @@
         <v>45415</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46898,7 +46902,7 @@
         <v>45141</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46971,7 +46975,7 @@
         <v>45071</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47044,7 +47048,7 @@
         <v>46253</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47117,7 +47121,7 @@
         <v>44963</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47190,7 +47194,7 @@
         <v>44992</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47268,7 +47272,7 @@
         <v>45169</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47346,7 +47350,7 @@
         <v>45153</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47419,7 +47423,7 @@
         <v>45329</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47492,7 +47496,7 @@
         <v>44963</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47565,7 +47569,7 @@
         <v>45090</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47643,7 +47647,7 @@
         <v>44699</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47716,7 +47720,7 @@
         <v>44582</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47789,7 +47793,7 @@
         <v>46251</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47862,7 +47866,7 @@
         <v>44582</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47935,7 +47939,7 @@
         <v>45386</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48008,7 +48012,7 @@
         <v>45462</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48081,7 +48085,7 @@
         <v>45328</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48159,7 +48163,7 @@
         <v>44691</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48232,7 +48236,7 @@
         <v>45050</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48310,7 +48314,7 @@
         <v>45636</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48383,7 +48387,7 @@
         <v>45674</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48456,7 +48460,7 @@
         <v>46295</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48529,7 +48533,7 @@
         <v>45593</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48602,7 +48606,7 @@
         <v>46301</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48675,7 +48679,7 @@
         <v>44825</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48748,7 +48752,7 @@
         <v>45698</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48821,7 +48825,7 @@
         <v>46301</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48894,7 +48898,7 @@
         <v>45461</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48967,7 +48971,7 @@
         <v>45517</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49040,7 +49044,7 @@
         <v>46155</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49113,7 +49117,7 @@
         <v>46260</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49191,7 +49195,7 @@
         <v>45674</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49264,7 +49268,7 @@
         <v>45646</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49337,7 +49341,7 @@
         <v>45229</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49415,7 +49419,7 @@
         <v>46261</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49488,7 +49492,7 @@
         <v>45798</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49561,7 +49565,7 @@
         <v>45231</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49634,7 +49638,7 @@
         <v>45560</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49707,7 +49711,7 @@
         <v>45798</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49780,7 +49784,7 @@
         <v>46307</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49853,7 +49857,7 @@
         <v>45240</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49931,7 +49935,7 @@
         <v>45799</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50004,7 +50008,7 @@
         <v>45799</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50077,7 +50081,7 @@
         <v>46126</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50150,7 +50154,7 @@
         <v>46135</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50223,7 +50227,7 @@
         <v>46307</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50296,7 +50300,7 @@
         <v>46307</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50369,7 +50373,7 @@
         <v>45813</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50442,7 +50446,7 @@
         <v>45798</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50515,7 +50519,7 @@
         <v>45531</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50588,7 +50592,7 @@
         <v>45810</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50661,7 +50665,7 @@
         <v>45822</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50734,7 +50738,7 @@
         <v>45835</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50807,7 +50811,7 @@
         <v>45841</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50885,7 +50889,7 @@
         <v>45700</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50958,7 +50962,7 @@
         <v>45772</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51031,7 +51035,7 @@
         <v>45852</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51104,7 +51108,7 @@
         <v>45852</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51177,7 +51181,7 @@
         <v>45845</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51250,7 +51254,7 @@
         <v>45729</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51323,7 +51327,7 @@
         <v>45875</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51396,7 +51400,7 @@
         <v>45105</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51469,7 +51473,7 @@
         <v>45257</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51542,7 +51546,7 @@
         <v>45098</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51615,7 +51619,7 @@
         <v>45474</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51708,7 +51712,7 @@
         <v>45345</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51781,7 +51785,7 @@
         <v>44980</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51879,7 +51883,7 @@
         <v>44903</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51952,7 +51956,7 @@
         <v>44658</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52025,7 +52029,7 @@
         <v>45714</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52103,7 +52107,7 @@
         <v>45531</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52176,7 +52180,7 @@
         <v>45798</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52249,7 +52253,7 @@
         <v>45946</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>46169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45852</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45057</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45649</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>45357</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44536</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44972</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45473</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45001</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45099</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44970</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45077</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45014</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>45184</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>45188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>44512</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>44839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>44500</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45903</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>46164</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>46010</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45013</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>46108</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>46111</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44995</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>44671</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45001</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>44823</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>44809</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45666</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45614</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>44719</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44546</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45898</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44995</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>46098</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44858</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44831</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>46183</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44995</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44872</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44749</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45001</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>45573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45666</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44889</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>46010</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>46009</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>46245</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>46251</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>46297</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45473</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45852</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>45183</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>44964</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45133</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>44875</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>45076</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45225</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>45231</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45103</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45345</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>46297</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44824</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44853</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44546</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44553</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44512</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44866</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>44628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44599</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44824</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44602</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44536</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44496</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44585</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44725</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44619</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44515</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44580</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44844</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44498</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44712</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>44783</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44783</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44510</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44783</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44495</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44496</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44683</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44571</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44607</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>44871</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44733</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44725</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44526</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44531</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44795</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44827</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44768</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45231</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44602</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44706</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>44837</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44838</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44872</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44725</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44797</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44496</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44789</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44605</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44641</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44848</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44616</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44522</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44832</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>44840</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44523</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44725</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44512</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44762</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44601</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44549</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44790</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44539</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44824</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44847</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44797</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45890</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45177</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45890</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44789</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44942</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44922</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44790</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45853</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45386</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44803</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44905</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>44694</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44691</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44859</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45595</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>44602</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45006</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45907</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44816</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44978</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45245</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>44708</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45222</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45075</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45547</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>46164</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45915</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46164</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44616</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45088</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>46101</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44957</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44694</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45268</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45925</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45071</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45946</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45174</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>44830</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45967</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45775</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>44978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45362</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44837</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45386</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44824</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44978</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>44978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>44830</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44830</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44888</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>44977</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44603</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45230</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44784</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44603</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>44607</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>46078</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44888</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>44888</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44701</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45208</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45100</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44952</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45019</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45457</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45106</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>44830</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>44871</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44789</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>44789</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45120</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45160</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44844</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>44886</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45415</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45950</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44977</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>45516</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44942</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44908</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45056</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45016</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46126</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45191</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46183</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>46126</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45214</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45033</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>46183</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45753</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>45126</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45456</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>46188</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44985</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>44974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>44945</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45154</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45205</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44886</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>45457</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44977</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>44855</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44934</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>44809</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>44825</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>46199</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>46199</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45281</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>46199</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46199</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>46199</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46199</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46199</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45214</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44830</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45316</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45646</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>45189</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45220</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45098</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>44957</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>44957</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44965</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>45692</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44495</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45601</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>45345</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45013</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44833</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45594</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45677</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45281</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45646</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>46000</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44945</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>46000</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45350</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45547</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>46002</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45478</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>46227</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45698</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>46232</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>46010</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46010</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45517</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46010</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45462</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45461</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46030</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>46244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>46037</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>46287</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45674</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45798</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45798</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45240</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>46287</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>46048</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45646</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45560</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45799</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45231</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>45799</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>46051</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44530</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>45509</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>44886</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>46245</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>44523</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>46126</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45813</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45798</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45531</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>46245</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>46245</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>46245</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45483</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44860</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45470</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44838</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46251</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45822</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>46073</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>46253</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>46084</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>46084</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>46084</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45835</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>46092</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45239</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46097</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45169</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>46097</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45478</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45841</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45475</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46098</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45700</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45772</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>46101</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45481</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>44840</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44858</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>46301</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45481</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45852</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45852</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45672</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>46106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>46111</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>46301</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>46260</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45088</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>46155</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>44602</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45729</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44602</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>46261</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>46126</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45875</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46126</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44596</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45393</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>46307</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>45483</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>46132</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>45727</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>46132</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>45518</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>45362</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>45460</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45362</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>46135</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45393</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>45393</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>44994</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>45852</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>44985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>44599</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>45357</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45902</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>46126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45229</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45786</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>45566</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45348</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45348</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45827</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45827</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>46307</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>44963</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45479</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44627</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>44811</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>46307</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>46136</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>46140</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45111</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45477</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45810</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44587</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44889</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45972</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>44502</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45785</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>46139</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>45477</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44957</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45636</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45870</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>46301</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>46310</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45964</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>46136</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>44985</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>44980</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>44659</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44995</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45594</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45594</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>46295</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>44928</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>46142</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>44623</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45384</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>46146</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45477</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>44733</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>44964</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>44984</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>44602</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>46150</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45590</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44725</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45272</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45247</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>44600</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45223</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45677</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45762</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45316</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44797</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45565</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>44701</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44701</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>45594</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>45204</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>44643</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45230</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>45593</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>45012</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>45061</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45001</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45001</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45000</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44968</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45594</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44987</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45096</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>45666</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>45041</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>45204</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>44795</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44781</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>44781</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45147</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45189</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>44817</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45226</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45688</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45098</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45182</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>45182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>44840</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>45205</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>44844</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44859</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>44862</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>45110</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44895</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45209</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>44909</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45050</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44862</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>44582</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>44963</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>45211</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>45231</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>45520</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>44852</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>45076</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>44559</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>44865</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45366</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45075</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45138</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>44848</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>44887</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42651,7 +42651,7 @@
         <v>44932</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45231</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45229</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>45450</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>45071</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45733</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45070</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>44859</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>44696</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44507</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45107</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45694</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45142</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>44551</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45393</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>44992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45327</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45329</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45322</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>44628</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45180</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>44601</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>45097</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45019</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45463</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45446</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>45393</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>45152</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45148</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>45478</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45105</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>44621</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45328</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45328</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45188,7 +45188,7 @@
         <v>45481</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>44985</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45328</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45533</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>45153</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44964</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>45125</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>45108</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>44596</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>44596</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>44582</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>44551</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>44551</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44609</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46215,7 +46215,7 @@
         <v>45211</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45338</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45517</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45632</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45230</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45077</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>45165</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45214</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>45050</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45692</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45674</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>44817</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45141</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45141</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>44699</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45215</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>45103</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45196</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>45090</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47637,7 +47637,7 @@
         <v>44678</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45446</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>45238</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>44664</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>44664</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>45124</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>44712</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>45096</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45169</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45153</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>44793</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45460</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>44823</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48591,7 +48591,7 @@
         <v>44760</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45163</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45357</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>44853</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>44518</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>44851</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45302</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45322</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>44895</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45268</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>44965</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>44519</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>45352</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45006</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45264</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49711,7 +49711,7 @@
         <v>44886</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>44888</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>45184</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>45357</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>45357</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45405</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45328</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>44831</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45547</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         <v>45328</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45167</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45026</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45478</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45181</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>45181</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>44776</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>44957</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>44858</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>44602</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51108,7 +51108,7 @@
         <v>45016</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45107</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>44691</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>45105</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>44658</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45257</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45098</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>45474</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51717,7 +51717,7 @@
         <v>45345</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>44980</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51888,7 +51888,7 @@
         <v>44903</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45714</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52039,7 +52039,7 @@
         <v>45531</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45798</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>45946</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>

--- a/Översikt KATRINEHOLM.xlsx
+++ b/Översikt KATRINEHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         <v>44642</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>44817</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44995</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>46169</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44876</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45057</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>45062</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45852</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45225</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>45057</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45099</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45649</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45926</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>45357</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44536</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44972</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45473</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45001</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45099</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44970</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45077</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45014</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>45184</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>45188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>44512</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>44839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>44500</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45903</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>46164</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>46010</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45013</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>46108</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>46111</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>44995</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>44671</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45001</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>44823</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>44809</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45666</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45614</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>44719</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44602</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44546</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44581</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45898</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44995</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>46098</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44858</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>44831</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>46183</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44995</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44872</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>44749</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45322</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45281</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45001</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>45573</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45666</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>44889</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>46010</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>46009</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>46245</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>46251</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>46297</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45473</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45852</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45852</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>45183</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>44964</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45133</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44803</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>44875</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>45076</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45225</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>45231</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45103</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45345</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>46297</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44824</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44853</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44546</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44553</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44512</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44866</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>44628</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44599</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44824</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44602</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44536</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44496</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44585</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44725</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>44791</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44619</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44515</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44580</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44844</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44498</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44712</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>44783</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44783</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44510</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>44783</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44495</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44496</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44683</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44571</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>44601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44607</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>44871</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44733</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44725</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44526</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44531</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44795</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44827</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44768</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45231</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44602</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44706</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>44837</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44838</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44872</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44725</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44797</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44496</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44789</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44605</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44641</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44848</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44616</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>44522</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44872</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44832</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>44840</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44523</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44725</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44512</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44762</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44601</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>44549</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>44790</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44539</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44824</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44847</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44797</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45890</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45177</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45890</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44789</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>44942</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44922</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44790</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45853</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45386</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44803</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>44905</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>44694</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44691</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44859</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45595</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>44602</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45006</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45907</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44816</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44978</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45245</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>44708</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45222</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45075</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45547</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>46164</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45915</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>46164</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44616</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45088</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>46101</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44957</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44694</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45268</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45925</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45071</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45946</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45174</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>44830</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45967</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45775</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>44978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45362</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44837</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45386</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44824</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44978</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>44978</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>44830</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>44830</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44888</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>44977</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>44603</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45230</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         <v>44784</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44603</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>44607</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>46078</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44888</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>44888</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44701</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45208</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45100</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44952</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45239</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45019</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45457</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45106</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>44830</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>44871</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>44789</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>44789</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45120</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45160</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44844</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>44886</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>45415</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>45950</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44977</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>45516</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>44942</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44908</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45056</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45016</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46126</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45191</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46183</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>46126</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45214</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45033</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>46183</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45753</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>45126</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45456</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>46188</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>44985</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>44974</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>44945</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45154</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45205</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>44886</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>45457</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44977</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>44855</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44934</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>44809</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>44825</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>46199</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>46199</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45281</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>46199</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46199</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>46199</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46199</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46199</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45214</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44830</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45316</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45646</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>45189</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45220</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45098</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>44957</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>44957</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44965</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>45692</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44495</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45601</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>45345</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45013</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44833</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45594</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45677</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45281</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45646</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>46000</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44945</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>46000</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45350</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45547</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>46002</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45478</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>46227</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45698</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>46232</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>46010</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46010</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45517</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46010</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45462</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45461</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46030</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>46244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>46037</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>46287</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45674</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45798</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45798</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45240</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>46287</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>46048</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45646</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45560</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>45799</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45231</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>45799</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>46051</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44530</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>45509</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>44886</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>46245</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>44523</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>46126</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45813</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45798</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>46248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45531</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>46245</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>46245</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>46245</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45483</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44860</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45470</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44838</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46251</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45822</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>46073</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>46253</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>46084</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>46084</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>46084</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45835</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>46092</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45239</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>46097</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45169</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>46097</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45478</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30409,7 +30409,7 @@
         <v>45841</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45475</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>46098</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45700</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45772</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>46101</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45481</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>44840</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44858</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>46301</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>45481</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>46107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45852</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45852</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45672</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>46106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>46111</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>46301</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>46260</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45088</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>46155</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>44602</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>45729</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>44602</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>46261</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>46126</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45875</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46126</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44596</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45393</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>46307</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>45483</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>46132</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>45727</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>46132</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33047,7 +33047,7 @@
         <v>45518</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>45362</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>45460</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45362</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>46135</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45393</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>45393</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>44994</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>45852</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>44985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>44599</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>45357</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45902</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>46126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>45229</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45786</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34220,7 +34220,7 @@
         <v>45566</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34293,7 +34293,7 @@
         <v>45348</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45348</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45827</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34512,7 +34512,7 @@
         <v>45827</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>46307</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>44963</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45479</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>44627</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>44811</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34950,7 +34950,7 @@
         <v>46307</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>46136</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>46140</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35169,7 +35169,7 @@
         <v>45111</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>45477</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45810</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44587</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>44889</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45972</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>44502</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45785</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>46139</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>45477</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44957</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45636</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45870</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>46301</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>46310</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45964</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>46136</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>44985</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>44980</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>44659</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44995</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45594</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45594</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>46295</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>44928</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>46142</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>44623</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45384</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>46146</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45477</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>44733</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>44964</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>44984</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>44602</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>46150</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45590</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44725</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45272</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45247</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>44600</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45223</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45677</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45762</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45316</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44797</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>45565</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>44701</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44701</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>45594</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>45204</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>44643</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45230</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>45593</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>45012</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>45061</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45001</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45001</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45000</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44968</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45594</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>44987</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45096</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>45666</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>45041</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>45204</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>44795</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44781</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>44781</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45147</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45189</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>44817</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>45226</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45688</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45098</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45182</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>45182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>44840</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>45205</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>44844</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>44859</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>44862</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>45110</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>44895</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45209</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>44909</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45050</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44862</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>44582</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>44963</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>45211</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>45231</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41921,7 +41921,7 @@
         <v>45520</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41994,7 +41994,7 @@
         <v>44852</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>45076</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>44559</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>44865</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45366</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45075</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45138</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>44848</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42578,7 +42578,7 @@
         <v>44887</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42651,7 +42651,7 @@
         <v>44932</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45231</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>45229</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>45450</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>45071</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45733</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45070</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>44859</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>44696</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>44507</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45107</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45694</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45142</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>44551</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>45393</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>44992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45327</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45329</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45322</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>44628</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45180</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>44601</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>45097</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45019</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45463</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45446</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>45393</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>45152</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45148</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>45478</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45105</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>44621</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45328</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45328</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45188,7 +45188,7 @@
         <v>45481</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>44985</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45334,7 +45334,7 @@
         <v>45328</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45533</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>45153</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>44964</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>45125</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45704,7 +45704,7 @@
         <v>45108</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>44596</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>44596</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>44582</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>44551</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>44551</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44609</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46215,7 +46215,7 @@
         <v>45211</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45338</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45517</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45632</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45230</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45077</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>45165</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45214</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>45050</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>45692</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>45674</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>44817</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47111,7 +47111,7 @@
         <v>45141</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45141</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>44699</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45215</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>45103</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45196</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>45090</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47637,7 +47637,7 @@
         <v>44678</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45446</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>45238</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>44664</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>44664</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>45124</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>44712</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>45096</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45169</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45153</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>44793</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45460</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>44823</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48591,7 +48591,7 @@
         <v>44760</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45163</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45357</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>44853</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>44518</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>44851</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45302</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45322</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>44895</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45268</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>44965</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>44519</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>45352</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49560,7 +49560,7 @@
         <v>45006</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45264</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49711,7 +49711,7 @@
         <v>44886</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>44888</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>45184</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>45357</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>45357</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45405</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45328</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>44831</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45547</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         <v>45328</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45167</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45026</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45478</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45181</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>45181</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>44776</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>44957</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>44858</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>44602</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51108,7 +51108,7 @@
         <v>45016</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51181,7 +51181,7 @@
         <v>45107</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>44691</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
         <v>45105</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>44658</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51478,7 +51478,7 @@
         <v>45257</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45098</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>45474</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51717,7 +51717,7 @@
         <v>45345</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>44980</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51888,7 +51888,7 @@
         <v>44903</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45714</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52039,7 +52039,7 @@
         <v>45531</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45798</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52185,7 +52185,7 @@
         <v>45946</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
